--- a/Data/Layout Types/Zada_layouts.xlsx
+++ b/Data/Layout Types/Zada_layouts.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/levan/Documents/MegaValuationer/Data/Layout Types/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BDD6DC-9D0B-C948-80B3-0E77055E5145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF018AC-E15C-164B-A0CD-10B78629091B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1260" windowWidth="27640" windowHeight="16740" xr2:uid="{DA252733-9A85-4B42-BBD3-A71084AF6D27}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="658">
   <si>
     <t>All Developments</t>
   </si>
@@ -2051,12 +2051,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2431,7 +2428,10 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1">
         <v>101</v>
       </c>
       <c r="E2" t="s">
@@ -2448,7 +2448,10 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2">
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1">
         <v>102</v>
       </c>
       <c r="E3" t="s">
@@ -2465,7 +2468,10 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1">
         <v>103</v>
       </c>
       <c r="E4" t="s">
@@ -2482,7 +2488,10 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1">
         <v>104</v>
       </c>
       <c r="E5" t="s">
@@ -2499,7 +2508,10 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
         <v>105</v>
       </c>
       <c r="E6" t="s">
@@ -2516,7 +2528,10 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="2">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
         <v>106</v>
       </c>
       <c r="E7" t="s">
@@ -2533,7 +2548,10 @@
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1">
         <v>107</v>
       </c>
       <c r="E8" t="s">
@@ -2550,7 +2568,10 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
         <v>108</v>
       </c>
       <c r="E9" t="s">
@@ -2567,7 +2588,10 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1">
         <v>109</v>
       </c>
       <c r="E10" t="s">
@@ -2584,7 +2608,10 @@
       <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="2">
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1">
         <v>110</v>
       </c>
       <c r="E11" t="s">
@@ -2601,7 +2628,10 @@
       <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="2">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
         <v>111</v>
       </c>
       <c r="E12" t="s">
@@ -2618,7 +2648,10 @@
       <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2">
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1">
         <v>112</v>
       </c>
       <c r="E13" t="s">
@@ -2635,7 +2668,10 @@
       <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="2">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1">
         <v>113</v>
       </c>
       <c r="E14" t="s">
@@ -2652,7 +2688,10 @@
       <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="2">
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1">
         <v>114</v>
       </c>
       <c r="E15" t="s">
@@ -2669,7 +2708,10 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="2">
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1">
         <v>115</v>
       </c>
       <c r="E16" t="s">
@@ -2686,7 +2728,10 @@
       <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="2">
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1">
         <v>116</v>
       </c>
       <c r="E17" t="s">
@@ -2703,7 +2748,10 @@
       <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="2">
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1">
         <v>117</v>
       </c>
       <c r="E18" t="s">
@@ -2720,7 +2768,10 @@
       <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="2">
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1">
         <v>118</v>
       </c>
       <c r="E19" t="s">
@@ -2737,7 +2788,10 @@
       <c r="B20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="2">
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1">
         <v>119</v>
       </c>
       <c r="E20" t="s">
@@ -2754,7 +2808,10 @@
       <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="2">
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" t="s">
@@ -2771,7 +2828,10 @@
       <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="2">
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1">
         <v>121</v>
       </c>
       <c r="E22" t="s">
@@ -2788,7 +2848,10 @@
       <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="2">
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="1">
         <v>122</v>
       </c>
       <c r="E23" t="s">
@@ -2805,7 +2868,10 @@
       <c r="B24" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="2">
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1">
         <v>123</v>
       </c>
       <c r="E24" t="s">
@@ -2822,7 +2888,10 @@
       <c r="B25" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="2">
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1">
         <v>124</v>
       </c>
       <c r="E25" t="s">
@@ -2839,7 +2908,10 @@
       <c r="B26" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="2">
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="1">
         <v>201</v>
       </c>
       <c r="E26" t="s">
@@ -2856,7 +2928,10 @@
       <c r="B27" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="2">
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1">
         <v>202</v>
       </c>
       <c r="E27" t="s">
@@ -2873,7 +2948,10 @@
       <c r="B28" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="2">
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1">
         <v>203</v>
       </c>
       <c r="E28" t="s">
@@ -2890,7 +2968,10 @@
       <c r="B29" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="1">
         <v>204</v>
       </c>
       <c r="E29" t="s">
@@ -2907,7 +2988,10 @@
       <c r="B30" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="2">
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1">
         <v>205</v>
       </c>
       <c r="E30" t="s">
@@ -2924,7 +3008,10 @@
       <c r="B31" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="2">
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1">
         <v>206</v>
       </c>
       <c r="E31" t="s">
@@ -2941,7 +3028,10 @@
       <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="2">
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1">
         <v>207</v>
       </c>
       <c r="E32" t="s">
@@ -2958,7 +3048,10 @@
       <c r="B33" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="2">
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1">
         <v>208</v>
       </c>
       <c r="E33" t="s">
@@ -2975,7 +3068,10 @@
       <c r="B34" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="2">
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1">
         <v>209</v>
       </c>
       <c r="E34" t="s">
@@ -2992,7 +3088,10 @@
       <c r="B35" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="2">
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1">
         <v>210</v>
       </c>
       <c r="E35" t="s">
@@ -3009,7 +3108,10 @@
       <c r="B36" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="2">
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1">
         <v>211</v>
       </c>
       <c r="E36" t="s">
@@ -3026,7 +3128,10 @@
       <c r="B37" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="2">
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1">
         <v>212</v>
       </c>
       <c r="E37" t="s">
@@ -3043,7 +3148,10 @@
       <c r="B38" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="2">
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1">
         <v>213</v>
       </c>
       <c r="E38" t="s">
@@ -3060,7 +3168,10 @@
       <c r="B39" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="2">
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1">
         <v>214</v>
       </c>
       <c r="E39" t="s">
@@ -3077,7 +3188,10 @@
       <c r="B40" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="2">
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1">
         <v>215</v>
       </c>
       <c r="E40" t="s">
@@ -3094,7 +3208,10 @@
       <c r="B41" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="2">
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1">
         <v>216</v>
       </c>
       <c r="E41" t="s">
@@ -3111,7 +3228,10 @@
       <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="2">
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1">
         <v>217</v>
       </c>
       <c r="E42" t="s">
@@ -3128,7 +3248,10 @@
       <c r="B43" t="s">
         <v>7</v>
       </c>
-      <c r="D43" s="2">
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="1">
         <v>218</v>
       </c>
       <c r="E43" t="s">
@@ -3145,7 +3268,10 @@
       <c r="B44" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="2">
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="1">
         <v>219</v>
       </c>
       <c r="E44" t="s">
@@ -3162,7 +3288,10 @@
       <c r="B45" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="2">
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1">
         <v>220</v>
       </c>
       <c r="E45" t="s">
@@ -3179,7 +3308,10 @@
       <c r="B46" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="2">
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1">
         <v>221</v>
       </c>
       <c r="E46" t="s">
@@ -3196,7 +3328,10 @@
       <c r="B47" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="2">
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="1">
         <v>222</v>
       </c>
       <c r="E47" t="s">
@@ -3213,7 +3348,10 @@
       <c r="B48" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="2">
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="1">
         <v>223</v>
       </c>
       <c r="E48" t="s">
@@ -3230,7 +3368,10 @@
       <c r="B49" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="2">
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="1">
         <v>224</v>
       </c>
       <c r="E49" t="s">
@@ -3247,7 +3388,10 @@
       <c r="B50" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="2">
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="1">
         <v>225</v>
       </c>
       <c r="E50" t="s">
@@ -3264,7 +3408,10 @@
       <c r="B51" t="s">
         <v>7</v>
       </c>
-      <c r="D51" s="2">
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="1">
         <v>226</v>
       </c>
       <c r="E51" t="s">
@@ -3281,7 +3428,10 @@
       <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="2">
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="1">
         <v>227</v>
       </c>
       <c r="E52" t="s">
@@ -3298,7 +3448,10 @@
       <c r="B53" t="s">
         <v>7</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
@@ -3315,7 +3468,10 @@
       <c r="B54" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
@@ -3332,7 +3488,10 @@
       <c r="B55" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
@@ -3349,7 +3508,10 @@
       <c r="B56" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E56" t="s">
@@ -3366,7 +3528,10 @@
       <c r="B57" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E57" t="s">
@@ -3383,7 +3548,10 @@
       <c r="B58" t="s">
         <v>7</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E58" t="s">
@@ -3400,7 +3568,10 @@
       <c r="B59" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E59" t="s">
@@ -3417,7 +3588,10 @@
       <c r="B60" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E60" t="s">
@@ -3434,7 +3608,10 @@
       <c r="B61" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
@@ -3451,7 +3628,10 @@
       <c r="B62" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E62" t="s">
@@ -3468,7 +3648,10 @@
       <c r="B63" t="s">
         <v>7</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E63" t="s">
@@ -3485,7 +3668,10 @@
       <c r="B64" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E64" t="s">
@@ -3502,7 +3688,10 @@
       <c r="B65" t="s">
         <v>7</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E65" t="s">
@@ -3519,7 +3708,10 @@
       <c r="B66" t="s">
         <v>7</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E66" t="s">
@@ -3536,7 +3728,10 @@
       <c r="B67" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E67" t="s">
@@ -3553,7 +3748,10 @@
       <c r="B68" t="s">
         <v>7</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E68" t="s">
@@ -3570,7 +3768,10 @@
       <c r="B69" t="s">
         <v>7</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E69" t="s">
@@ -3587,7 +3788,10 @@
       <c r="B70" t="s">
         <v>7</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E70" t="s">
@@ -3604,7 +3808,10 @@
       <c r="B71" t="s">
         <v>7</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E71" t="s">
@@ -3621,7 +3828,10 @@
       <c r="B72" t="s">
         <v>7</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E72" t="s">
@@ -3638,7 +3848,10 @@
       <c r="B73" t="s">
         <v>7</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E73" t="s">
@@ -3655,7 +3868,10 @@
       <c r="B74" t="s">
         <v>7</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E74" t="s">
@@ -3672,7 +3888,10 @@
       <c r="B75" t="s">
         <v>7</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E75" t="s">
@@ -3689,7 +3908,10 @@
       <c r="B76" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E76" t="s">
@@ -3706,7 +3928,10 @@
       <c r="B77" t="s">
         <v>7</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E77" t="s">
@@ -3723,7 +3948,10 @@
       <c r="B78" t="s">
         <v>7</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E78" t="s">
@@ -3740,7 +3968,10 @@
       <c r="B79" t="s">
         <v>7</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E79" t="s">
@@ -3757,7 +3988,10 @@
       <c r="B80" t="s">
         <v>7</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E80" t="s">
@@ -3774,7 +4008,10 @@
       <c r="B81" t="s">
         <v>7</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="C81" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E81" t="s">
@@ -3791,7 +4028,10 @@
       <c r="B82" t="s">
         <v>7</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E82" t="s">
@@ -3808,7 +4048,10 @@
       <c r="B83" t="s">
         <v>7</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E83" t="s">
@@ -3825,7 +4068,10 @@
       <c r="B84" t="s">
         <v>7</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E84" t="s">
@@ -3842,7 +4088,10 @@
       <c r="B85" t="s">
         <v>7</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E85" t="s">
@@ -3859,7 +4108,10 @@
       <c r="B86" t="s">
         <v>7</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E86" t="s">
@@ -3876,7 +4128,10 @@
       <c r="B87" t="s">
         <v>7</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="C87" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E87" t="s">
@@ -3893,7 +4148,10 @@
       <c r="B88" t="s">
         <v>7</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E88" t="s">
@@ -3910,7 +4168,10 @@
       <c r="B89" t="s">
         <v>7</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E89" t="s">
@@ -3927,7 +4188,10 @@
       <c r="B90" t="s">
         <v>7</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E90" t="s">
@@ -3944,7 +4208,10 @@
       <c r="B91" t="s">
         <v>7</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E91" t="s">
@@ -3961,7 +4228,10 @@
       <c r="B92" t="s">
         <v>7</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E92" t="s">
@@ -3978,7 +4248,10 @@
       <c r="B93" t="s">
         <v>7</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E93" t="s">
@@ -3995,7 +4268,10 @@
       <c r="B94" t="s">
         <v>7</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E94" t="s">
@@ -4012,7 +4288,10 @@
       <c r="B95" t="s">
         <v>7</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="C95" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E95" t="s">
@@ -4029,7 +4308,10 @@
       <c r="B96" t="s">
         <v>7</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="C96" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E96" t="s">
@@ -4046,7 +4328,10 @@
       <c r="B97" t="s">
         <v>7</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="C97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E97" t="s">
@@ -4063,7 +4348,10 @@
       <c r="B98" t="s">
         <v>7</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E98" t="s">
@@ -4080,7 +4368,10 @@
       <c r="B99" t="s">
         <v>7</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E99" t="s">
@@ -4097,7 +4388,10 @@
       <c r="B100" t="s">
         <v>7</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="C100" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E100" t="s">
@@ -4114,7 +4408,10 @@
       <c r="B101" t="s">
         <v>7</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="C101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E101" t="s">
@@ -4131,7 +4428,10 @@
       <c r="B102" t="s">
         <v>7</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E102" t="s">
@@ -4148,7 +4448,10 @@
       <c r="B103" t="s">
         <v>7</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E103" t="s">
@@ -4165,7 +4468,10 @@
       <c r="B104" t="s">
         <v>7</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E104" t="s">
@@ -4182,7 +4488,10 @@
       <c r="B105" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E105" t="s">
@@ -4199,7 +4508,10 @@
       <c r="B106" t="s">
         <v>7</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E106" t="s">
@@ -4216,7 +4528,10 @@
       <c r="B107" t="s">
         <v>7</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E107" t="s">
@@ -4233,7 +4548,10 @@
       <c r="B108" t="s">
         <v>7</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E108" t="s">
@@ -4250,7 +4568,10 @@
       <c r="B109" t="s">
         <v>7</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E109" t="s">
@@ -4267,7 +4588,10 @@
       <c r="B110" t="s">
         <v>7</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E110" t="s">
@@ -4284,7 +4608,10 @@
       <c r="B111" t="s">
         <v>7</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E111" t="s">
@@ -4301,7 +4628,10 @@
       <c r="B112" t="s">
         <v>7</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E112" t="s">
@@ -4318,7 +4648,10 @@
       <c r="B113" t="s">
         <v>7</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E113" t="s">
@@ -4335,7 +4668,10 @@
       <c r="B114" t="s">
         <v>7</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E114" t="s">
@@ -4352,7 +4688,10 @@
       <c r="B115" t="s">
         <v>7</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E115" t="s">
@@ -4369,7 +4708,10 @@
       <c r="B116" t="s">
         <v>7</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E116" t="s">
@@ -4386,7 +4728,10 @@
       <c r="B117" t="s">
         <v>7</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E117" t="s">
@@ -4403,7 +4748,10 @@
       <c r="B118" t="s">
         <v>7</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E118" t="s">
@@ -4420,7 +4768,10 @@
       <c r="B119" t="s">
         <v>7</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E119" t="s">
@@ -4437,7 +4788,10 @@
       <c r="B120" t="s">
         <v>7</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>77</v>
       </c>
       <c r="E120" t="s">
@@ -4454,7 +4808,10 @@
       <c r="B121" t="s">
         <v>7</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E121" t="s">
@@ -4471,7 +4828,10 @@
       <c r="B122" t="s">
         <v>7</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E122" t="s">
@@ -4488,7 +4848,10 @@
       <c r="B123" t="s">
         <v>7</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E123" t="s">
@@ -4505,7 +4868,10 @@
       <c r="B124" t="s">
         <v>7</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E124" t="s">
@@ -4522,7 +4888,10 @@
       <c r="B125" t="s">
         <v>7</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="C125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E125" t="s">
@@ -4539,7 +4908,10 @@
       <c r="B126" t="s">
         <v>7</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="C126" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E126" t="s">
@@ -4556,7 +4928,10 @@
       <c r="B127" t="s">
         <v>7</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E127" t="s">
@@ -4573,7 +4948,10 @@
       <c r="B128" t="s">
         <v>7</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E128" t="s">
@@ -4590,7 +4968,10 @@
       <c r="B129" t="s">
         <v>7</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E129" t="s">
@@ -4607,7 +4988,10 @@
       <c r="B130" t="s">
         <v>7</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E130" t="s">
@@ -4624,7 +5008,10 @@
       <c r="B131" t="s">
         <v>7</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E131" t="s">
@@ -4641,7 +5028,10 @@
       <c r="B132" t="s">
         <v>7</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E132" t="s">
@@ -4658,7 +5048,10 @@
       <c r="B133" t="s">
         <v>7</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E133" t="s">
@@ -4675,7 +5068,10 @@
       <c r="B134" t="s">
         <v>7</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E134" t="s">
@@ -4692,7 +5088,10 @@
       <c r="B135" t="s">
         <v>7</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E135" t="s">
@@ -4709,7 +5108,10 @@
       <c r="B136" t="s">
         <v>7</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>93</v>
       </c>
       <c r="E136" t="s">
@@ -4726,7 +5128,10 @@
       <c r="B137" t="s">
         <v>7</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E137" t="s">
@@ -4743,7 +5148,10 @@
       <c r="B138" t="s">
         <v>7</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E138" t="s">
@@ -4760,7 +5168,10 @@
       <c r="B139" t="s">
         <v>7</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E139" t="s">
@@ -4777,7 +5188,10 @@
       <c r="B140" t="s">
         <v>7</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E140" t="s">
@@ -4794,7 +5208,10 @@
       <c r="B141" t="s">
         <v>7</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E141" t="s">
@@ -4811,7 +5228,10 @@
       <c r="B142" t="s">
         <v>7</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="C142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>99</v>
       </c>
       <c r="E142" t="s">
@@ -4828,7 +5248,10 @@
       <c r="B143" t="s">
         <v>7</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E143" t="s">
@@ -4845,7 +5268,10 @@
       <c r="B144" t="s">
         <v>7</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E144" t="s">
@@ -4862,7 +5288,10 @@
       <c r="B145" t="s">
         <v>7</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E145" t="s">
@@ -4879,7 +5308,10 @@
       <c r="B146" t="s">
         <v>7</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="C146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E146" t="s">
@@ -4896,7 +5328,10 @@
       <c r="B147" t="s">
         <v>7</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E147" t="s">
@@ -4913,7 +5348,10 @@
       <c r="B148" t="s">
         <v>7</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E148" t="s">
@@ -4930,7 +5368,10 @@
       <c r="B149" t="s">
         <v>7</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E149" t="s">
@@ -4947,7 +5388,10 @@
       <c r="B150" t="s">
         <v>7</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E150" t="s">
@@ -4964,7 +5408,10 @@
       <c r="B151" t="s">
         <v>7</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E151" t="s">
@@ -4981,7 +5428,10 @@
       <c r="B152" t="s">
         <v>7</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="C152" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E152" t="s">
@@ -4998,7 +5448,10 @@
       <c r="B153" t="s">
         <v>7</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>110</v>
       </c>
       <c r="E153" t="s">
@@ -5015,7 +5468,10 @@
       <c r="B154" t="s">
         <v>7</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E154" t="s">
@@ -5032,7 +5488,10 @@
       <c r="B155" t="s">
         <v>7</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="C155" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E155" t="s">
@@ -5049,7 +5508,10 @@
       <c r="B156" t="s">
         <v>7</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="C156" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>113</v>
       </c>
       <c r="E156" t="s">
@@ -5066,7 +5528,10 @@
       <c r="B157" t="s">
         <v>7</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="C157" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E157" t="s">
@@ -5083,7 +5548,10 @@
       <c r="B158" t="s">
         <v>7</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="C158" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>115</v>
       </c>
       <c r="E158" t="s">
@@ -5100,7 +5568,10 @@
       <c r="B159" t="s">
         <v>7</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>116</v>
       </c>
       <c r="E159" t="s">
@@ -5117,7 +5588,10 @@
       <c r="B160" t="s">
         <v>7</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="C160" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E160" t="s">
@@ -5134,7 +5608,10 @@
       <c r="B161" t="s">
         <v>7</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="C161" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E161" t="s">
@@ -5151,7 +5628,10 @@
       <c r="B162" t="s">
         <v>7</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="C162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E162" t="s">
@@ -5168,7 +5648,10 @@
       <c r="B163" t="s">
         <v>7</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>120</v>
       </c>
       <c r="E163" t="s">
@@ -5185,7 +5668,10 @@
       <c r="B164" t="s">
         <v>7</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="C164" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E164" t="s">
@@ -5202,7 +5688,10 @@
       <c r="B165" t="s">
         <v>7</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>122</v>
       </c>
       <c r="E165" t="s">
@@ -5219,7 +5708,10 @@
       <c r="B166" t="s">
         <v>7</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="C166" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>123</v>
       </c>
       <c r="E166" t="s">
@@ -5236,7 +5728,10 @@
       <c r="B167" t="s">
         <v>7</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="C167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E167" t="s">
@@ -5253,7 +5748,10 @@
       <c r="B168" t="s">
         <v>7</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="C168" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E168" t="s">
@@ -5270,7 +5768,10 @@
       <c r="B169" t="s">
         <v>7</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>126</v>
       </c>
       <c r="E169" t="s">
@@ -5287,7 +5788,10 @@
       <c r="B170" t="s">
         <v>7</v>
       </c>
-      <c r="D170" s="2" t="s">
+      <c r="C170" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>127</v>
       </c>
       <c r="E170" t="s">
@@ -5304,7 +5808,10 @@
       <c r="B171" t="s">
         <v>7</v>
       </c>
-      <c r="D171" s="2" t="s">
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>128</v>
       </c>
       <c r="E171" t="s">
@@ -5321,7 +5828,10 @@
       <c r="B172" t="s">
         <v>7</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>129</v>
       </c>
       <c r="E172" t="s">
@@ -5338,7 +5848,10 @@
       <c r="B173" t="s">
         <v>7</v>
       </c>
-      <c r="D173" s="2" t="s">
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E173" t="s">
@@ -5355,7 +5868,10 @@
       <c r="B174" t="s">
         <v>7</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>131</v>
       </c>
       <c r="E174" t="s">
@@ -5372,7 +5888,10 @@
       <c r="B175" t="s">
         <v>7</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>132</v>
       </c>
       <c r="E175" t="s">
@@ -5389,7 +5908,10 @@
       <c r="B176" t="s">
         <v>7</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="C176" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E176" t="s">
@@ -5406,7 +5928,10 @@
       <c r="B177" t="s">
         <v>7</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>134</v>
       </c>
       <c r="E177" t="s">
@@ -5423,7 +5948,10 @@
       <c r="B178" t="s">
         <v>7</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>135</v>
       </c>
       <c r="E178" t="s">
@@ -5440,7 +5968,10 @@
       <c r="B179" t="s">
         <v>7</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>136</v>
       </c>
       <c r="E179" t="s">
@@ -5457,7 +5988,10 @@
       <c r="B180" t="s">
         <v>7</v>
       </c>
-      <c r="D180" s="2" t="s">
+      <c r="C180" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E180" t="s">
@@ -5474,7 +6008,10 @@
       <c r="B181" t="s">
         <v>7</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="C181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E181" t="s">
@@ -5491,7 +6028,10 @@
       <c r="B182" t="s">
         <v>7</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="C182" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E182" t="s">
@@ -5508,7 +6048,10 @@
       <c r="B183" t="s">
         <v>7</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>140</v>
       </c>
       <c r="E183" t="s">
@@ -5525,7 +6068,10 @@
       <c r="B184" t="s">
         <v>7</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>141</v>
       </c>
       <c r="E184" t="s">
@@ -5542,7 +6088,10 @@
       <c r="B185" t="s">
         <v>7</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="C185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E185" t="s">
@@ -5559,7 +6108,10 @@
       <c r="B186" t="s">
         <v>7</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="C186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E186" t="s">
@@ -5576,7 +6128,10 @@
       <c r="B187" t="s">
         <v>7</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E187" t="s">
@@ -5593,7 +6148,10 @@
       <c r="B188" t="s">
         <v>7</v>
       </c>
-      <c r="D188" s="2" t="s">
+      <c r="C188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>145</v>
       </c>
       <c r="E188" t="s">
@@ -5610,7 +6168,10 @@
       <c r="B189" t="s">
         <v>7</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>146</v>
       </c>
       <c r="E189" t="s">
@@ -5627,7 +6188,10 @@
       <c r="B190" t="s">
         <v>7</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="C190" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>147</v>
       </c>
       <c r="E190" t="s">
@@ -5644,7 +6208,10 @@
       <c r="B191" t="s">
         <v>7</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="C191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>148</v>
       </c>
       <c r="E191" t="s">
@@ -5661,7 +6228,10 @@
       <c r="B192" t="s">
         <v>7</v>
       </c>
-      <c r="D192" s="2" t="s">
+      <c r="C192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E192" t="s">
@@ -5678,7 +6248,10 @@
       <c r="B193" t="s">
         <v>7</v>
       </c>
-      <c r="D193" s="2" t="s">
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E193" t="s">
@@ -5695,7 +6268,10 @@
       <c r="B194" t="s">
         <v>7</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E194" t="s">
@@ -5712,7 +6288,10 @@
       <c r="B195" t="s">
         <v>7</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>152</v>
       </c>
       <c r="E195" t="s">
@@ -5729,7 +6308,10 @@
       <c r="B196" t="s">
         <v>7</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="C196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E196" t="s">
@@ -5746,7 +6328,10 @@
       <c r="B197" t="s">
         <v>7</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="C197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E197" t="s">
@@ -5763,7 +6348,10 @@
       <c r="B198" t="s">
         <v>7</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="C198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E198" t="s">
@@ -5780,7 +6368,10 @@
       <c r="B199" t="s">
         <v>7</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>156</v>
       </c>
       <c r="E199" t="s">
@@ -5797,7 +6388,10 @@
       <c r="B200" t="s">
         <v>7</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>157</v>
       </c>
       <c r="E200" t="s">
@@ -5814,7 +6408,10 @@
       <c r="B201" t="s">
         <v>7</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>158</v>
       </c>
       <c r="E201" t="s">
@@ -5831,7 +6428,10 @@
       <c r="B202" t="s">
         <v>7</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>159</v>
       </c>
       <c r="E202" t="s">
@@ -5848,7 +6448,10 @@
       <c r="B203" t="s">
         <v>7</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E203" t="s">
@@ -5865,7 +6468,10 @@
       <c r="B204" t="s">
         <v>7</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E204" t="s">
@@ -5882,7 +6488,10 @@
       <c r="B205" t="s">
         <v>7</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E205" t="s">
@@ -5899,7 +6508,10 @@
       <c r="B206" t="s">
         <v>7</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>163</v>
       </c>
       <c r="E206" t="s">
@@ -5916,7 +6528,10 @@
       <c r="B207" t="s">
         <v>7</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>164</v>
       </c>
       <c r="E207" t="s">
@@ -5933,7 +6548,10 @@
       <c r="B208" t="s">
         <v>7</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>165</v>
       </c>
       <c r="E208" t="s">
@@ -5950,7 +6568,10 @@
       <c r="B209" t="s">
         <v>7</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>166</v>
       </c>
       <c r="E209" t="s">
@@ -5967,7 +6588,10 @@
       <c r="B210" t="s">
         <v>7</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>167</v>
       </c>
       <c r="E210" t="s">
@@ -5984,7 +6608,10 @@
       <c r="B211" t="s">
         <v>7</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>168</v>
       </c>
       <c r="E211" t="s">
@@ -6001,7 +6628,10 @@
       <c r="B212" t="s">
         <v>7</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>169</v>
       </c>
       <c r="E212" t="s">
@@ -6018,7 +6648,10 @@
       <c r="B213" t="s">
         <v>7</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>170</v>
       </c>
       <c r="E213" t="s">
@@ -6035,7 +6668,10 @@
       <c r="B214" t="s">
         <v>7</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E214" t="s">
@@ -6052,7 +6688,10 @@
       <c r="B215" t="s">
         <v>7</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E215" t="s">
@@ -6069,7 +6708,10 @@
       <c r="B216" t="s">
         <v>7</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>173</v>
       </c>
       <c r="E216" t="s">
@@ -6086,7 +6728,10 @@
       <c r="B217" t="s">
         <v>7</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>174</v>
       </c>
       <c r="E217" t="s">
@@ -6103,7 +6748,10 @@
       <c r="B218" t="s">
         <v>7</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="C218" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>175</v>
       </c>
       <c r="E218" t="s">
@@ -6120,7 +6768,10 @@
       <c r="B219" t="s">
         <v>7</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>176</v>
       </c>
       <c r="E219" t="s">
@@ -6137,7 +6788,10 @@
       <c r="B220" t="s">
         <v>7</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="C220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>177</v>
       </c>
       <c r="E220" t="s">
@@ -6154,7 +6808,10 @@
       <c r="B221" t="s">
         <v>7</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E221" t="s">
@@ -6171,7 +6828,10 @@
       <c r="B222" t="s">
         <v>7</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="C222" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>179</v>
       </c>
       <c r="E222" t="s">
@@ -6188,7 +6848,10 @@
       <c r="B223" t="s">
         <v>7</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E223" t="s">
@@ -6205,7 +6868,10 @@
       <c r="B224" t="s">
         <v>7</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="C224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>181</v>
       </c>
       <c r="E224" t="s">
@@ -6222,7 +6888,10 @@
       <c r="B225" t="s">
         <v>7</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>182</v>
       </c>
       <c r="E225" t="s">
@@ -6239,7 +6908,10 @@
       <c r="B226" t="s">
         <v>7</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="C226" t="s">
+        <v>7</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>183</v>
       </c>
       <c r="E226" t="s">
@@ -6256,7 +6928,10 @@
       <c r="B227" t="s">
         <v>7</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="C227" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>184</v>
       </c>
       <c r="E227" t="s">
@@ -6273,7 +6948,10 @@
       <c r="B228" t="s">
         <v>7</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="C228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>185</v>
       </c>
       <c r="E228" t="s">
@@ -6290,7 +6968,10 @@
       <c r="B229" t="s">
         <v>7</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>186</v>
       </c>
       <c r="E229" t="s">
@@ -6307,7 +6988,10 @@
       <c r="B230" t="s">
         <v>7</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="C230" t="s">
+        <v>7</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>187</v>
       </c>
       <c r="E230" t="s">
@@ -6324,7 +7008,10 @@
       <c r="B231" t="s">
         <v>7</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="C231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>188</v>
       </c>
       <c r="E231" t="s">
@@ -6341,7 +7028,10 @@
       <c r="B232" t="s">
         <v>7</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="C232" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>189</v>
       </c>
       <c r="E232" t="s">
@@ -6358,7 +7048,10 @@
       <c r="B233" t="s">
         <v>7</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="C233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>190</v>
       </c>
       <c r="E233" t="s">
@@ -6375,7 +7068,10 @@
       <c r="B234" t="s">
         <v>7</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>191</v>
       </c>
       <c r="E234" t="s">
@@ -6392,7 +7088,10 @@
       <c r="B235" t="s">
         <v>7</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="C235" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>192</v>
       </c>
       <c r="E235" t="s">
@@ -6409,7 +7108,10 @@
       <c r="B236" t="s">
         <v>7</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="C236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>193</v>
       </c>
       <c r="E236" t="s">
@@ -6426,7 +7128,10 @@
       <c r="B237" t="s">
         <v>7</v>
       </c>
-      <c r="D237" s="2" t="s">
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>194</v>
       </c>
       <c r="E237" t="s">
@@ -6443,7 +7148,10 @@
       <c r="B238" t="s">
         <v>7</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="C238" t="s">
+        <v>7</v>
+      </c>
+      <c r="D238" s="1" t="s">
         <v>195</v>
       </c>
       <c r="E238" t="s">
@@ -6460,7 +7168,10 @@
       <c r="B239" t="s">
         <v>7</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>196</v>
       </c>
       <c r="E239" t="s">
@@ -6477,7 +7188,10 @@
       <c r="B240" t="s">
         <v>7</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="C240" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>197</v>
       </c>
       <c r="E240" t="s">
@@ -6494,7 +7208,10 @@
       <c r="B241" t="s">
         <v>7</v>
       </c>
-      <c r="D241" s="2" t="s">
+      <c r="C241" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" s="1" t="s">
         <v>198</v>
       </c>
       <c r="E241" t="s">
@@ -6511,7 +7228,10 @@
       <c r="B242" t="s">
         <v>7</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="C242" t="s">
+        <v>7</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>199</v>
       </c>
       <c r="E242" t="s">
@@ -6528,7 +7248,10 @@
       <c r="B243" t="s">
         <v>7</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="C243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>200</v>
       </c>
       <c r="E243" t="s">
@@ -6545,7 +7268,10 @@
       <c r="B244" t="s">
         <v>7</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="C244" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>201</v>
       </c>
       <c r="E244" t="s">
@@ -6562,7 +7288,10 @@
       <c r="B245" t="s">
         <v>7</v>
       </c>
-      <c r="D245" s="2" t="s">
+      <c r="C245" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>202</v>
       </c>
       <c r="E245" t="s">
@@ -6579,7 +7308,10 @@
       <c r="B246" t="s">
         <v>7</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="C246" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>203</v>
       </c>
       <c r="E246" t="s">
@@ -6596,7 +7328,10 @@
       <c r="B247" t="s">
         <v>7</v>
       </c>
-      <c r="D247" s="2" t="s">
+      <c r="C247" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>204</v>
       </c>
       <c r="E247" t="s">
@@ -6613,7 +7348,10 @@
       <c r="B248" t="s">
         <v>7</v>
       </c>
-      <c r="D248" s="2" t="s">
+      <c r="C248" t="s">
+        <v>7</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>205</v>
       </c>
       <c r="E248" t="s">
@@ -6630,7 +7368,10 @@
       <c r="B249" t="s">
         <v>7</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>206</v>
       </c>
       <c r="E249" t="s">
@@ -6647,7 +7388,10 @@
       <c r="B250" t="s">
         <v>7</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="C250" t="s">
+        <v>7</v>
+      </c>
+      <c r="D250" s="1" t="s">
         <v>207</v>
       </c>
       <c r="E250" t="s">
@@ -6664,7 +7408,10 @@
       <c r="B251" t="s">
         <v>7</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="C251" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>208</v>
       </c>
       <c r="E251" t="s">
@@ -6681,7 +7428,10 @@
       <c r="B252" t="s">
         <v>7</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="C252" t="s">
+        <v>7</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>209</v>
       </c>
       <c r="E252" t="s">
@@ -6698,7 +7448,10 @@
       <c r="B253" t="s">
         <v>7</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="C253" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E253" t="s">
@@ -6715,7 +7468,10 @@
       <c r="B254" t="s">
         <v>7</v>
       </c>
-      <c r="D254" s="2" t="s">
+      <c r="C254" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>211</v>
       </c>
       <c r="E254" t="s">
@@ -6732,7 +7488,10 @@
       <c r="B255" t="s">
         <v>7</v>
       </c>
-      <c r="D255" s="2" t="s">
+      <c r="C255" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>212</v>
       </c>
       <c r="E255" t="s">
@@ -6749,7 +7508,10 @@
       <c r="B256" t="s">
         <v>7</v>
       </c>
-      <c r="D256" s="2" t="s">
+      <c r="C256" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>213</v>
       </c>
       <c r="E256" t="s">
@@ -6766,7 +7528,10 @@
       <c r="B257" t="s">
         <v>7</v>
       </c>
-      <c r="D257" s="2" t="s">
+      <c r="C257" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>214</v>
       </c>
       <c r="E257" t="s">
@@ -6783,7 +7548,10 @@
       <c r="B258" t="s">
         <v>7</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="C258" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>215</v>
       </c>
       <c r="E258" t="s">
@@ -6800,7 +7568,10 @@
       <c r="B259" t="s">
         <v>7</v>
       </c>
-      <c r="D259" s="2" t="s">
+      <c r="C259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>216</v>
       </c>
       <c r="E259" t="s">
@@ -6817,7 +7588,10 @@
       <c r="B260" t="s">
         <v>7</v>
       </c>
-      <c r="D260" s="2" t="s">
+      <c r="C260" t="s">
+        <v>7</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>217</v>
       </c>
       <c r="E260" t="s">
@@ -6834,7 +7608,10 @@
       <c r="B261" t="s">
         <v>7</v>
       </c>
-      <c r="D261" s="2" t="s">
+      <c r="C261" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>218</v>
       </c>
       <c r="E261" t="s">
@@ -6851,7 +7628,10 @@
       <c r="B262" t="s">
         <v>7</v>
       </c>
-      <c r="D262" s="2" t="s">
+      <c r="C262" t="s">
+        <v>7</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>219</v>
       </c>
       <c r="E262" t="s">
@@ -6868,7 +7648,10 @@
       <c r="B263" t="s">
         <v>7</v>
       </c>
-      <c r="D263" s="2" t="s">
+      <c r="C263" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>220</v>
       </c>
       <c r="E263" t="s">
@@ -6885,7 +7668,10 @@
       <c r="B264" t="s">
         <v>7</v>
       </c>
-      <c r="D264" s="2" t="s">
+      <c r="C264" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>221</v>
       </c>
       <c r="E264" t="s">
@@ -6902,7 +7688,10 @@
       <c r="B265" t="s">
         <v>7</v>
       </c>
-      <c r="D265" s="2" t="s">
+      <c r="C265" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>222</v>
       </c>
       <c r="E265" t="s">
@@ -6919,7 +7708,10 @@
       <c r="B266" t="s">
         <v>7</v>
       </c>
-      <c r="D266" s="2" t="s">
+      <c r="C266" t="s">
+        <v>7</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>223</v>
       </c>
       <c r="E266" t="s">
@@ -6936,7 +7728,10 @@
       <c r="B267" t="s">
         <v>7</v>
       </c>
-      <c r="D267" s="2" t="s">
+      <c r="C267" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E267" t="s">
@@ -6953,7 +7748,10 @@
       <c r="B268" t="s">
         <v>7</v>
       </c>
-      <c r="D268" s="2" t="s">
+      <c r="C268" t="s">
+        <v>7</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>225</v>
       </c>
       <c r="E268" t="s">
@@ -6970,7 +7768,10 @@
       <c r="B269" t="s">
         <v>7</v>
       </c>
-      <c r="D269" s="2" t="s">
+      <c r="C269" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E269" t="s">
@@ -6987,7 +7788,10 @@
       <c r="B270" t="s">
         <v>7</v>
       </c>
-      <c r="D270" s="2" t="s">
+      <c r="C270" t="s">
+        <v>7</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>227</v>
       </c>
       <c r="E270" t="s">
@@ -7004,7 +7808,10 @@
       <c r="B271" t="s">
         <v>7</v>
       </c>
-      <c r="D271" s="2" t="s">
+      <c r="C271" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E271" t="s">
@@ -7021,7 +7828,10 @@
       <c r="B272" t="s">
         <v>7</v>
       </c>
-      <c r="D272" s="2" t="s">
+      <c r="C272" t="s">
+        <v>7</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>229</v>
       </c>
       <c r="E272" t="s">
@@ -7038,7 +7848,10 @@
       <c r="B273" t="s">
         <v>7</v>
       </c>
-      <c r="D273" s="2" t="s">
+      <c r="C273" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>230</v>
       </c>
       <c r="E273" t="s">
@@ -7055,7 +7868,10 @@
       <c r="B274" t="s">
         <v>7</v>
       </c>
-      <c r="D274" s="2" t="s">
+      <c r="C274" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>231</v>
       </c>
       <c r="E274" t="s">
@@ -7072,7 +7888,10 @@
       <c r="B275" t="s">
         <v>7</v>
       </c>
-      <c r="D275" s="2" t="s">
+      <c r="C275" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>232</v>
       </c>
       <c r="E275" t="s">
@@ -7089,7 +7908,10 @@
       <c r="B276" t="s">
         <v>7</v>
       </c>
-      <c r="D276" s="2" t="s">
+      <c r="C276" t="s">
+        <v>7</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>233</v>
       </c>
       <c r="E276" t="s">
@@ -7106,7 +7928,10 @@
       <c r="B277" t="s">
         <v>7</v>
       </c>
-      <c r="D277" s="2" t="s">
+      <c r="C277" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>234</v>
       </c>
       <c r="E277" t="s">
@@ -7123,7 +7948,10 @@
       <c r="B278" t="s">
         <v>7</v>
       </c>
-      <c r="D278" s="2" t="s">
+      <c r="C278" t="s">
+        <v>7</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>235</v>
       </c>
       <c r="E278" t="s">
@@ -7140,7 +7968,10 @@
       <c r="B279" t="s">
         <v>7</v>
       </c>
-      <c r="D279" s="2" t="s">
+      <c r="C279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>236</v>
       </c>
       <c r="E279" t="s">
@@ -7157,7 +7988,10 @@
       <c r="B280" t="s">
         <v>7</v>
       </c>
-      <c r="D280" s="2" t="s">
+      <c r="C280" t="s">
+        <v>7</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E280" t="s">
@@ -7174,7 +8008,10 @@
       <c r="B281" t="s">
         <v>7</v>
       </c>
-      <c r="D281" s="2" t="s">
+      <c r="C281" t="s">
+        <v>7</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>238</v>
       </c>
       <c r="E281" t="s">
@@ -7191,7 +8028,10 @@
       <c r="B282" t="s">
         <v>7</v>
       </c>
-      <c r="D282" s="2" t="s">
+      <c r="C282" t="s">
+        <v>7</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>239</v>
       </c>
       <c r="E282" t="s">
@@ -7208,7 +8048,10 @@
       <c r="B283" t="s">
         <v>7</v>
       </c>
-      <c r="D283" s="2" t="s">
+      <c r="C283" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>240</v>
       </c>
       <c r="E283" t="s">
@@ -7225,7 +8068,10 @@
       <c r="B284" t="s">
         <v>7</v>
       </c>
-      <c r="D284" s="2" t="s">
+      <c r="C284" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>241</v>
       </c>
       <c r="E284" t="s">
@@ -7242,7 +8088,10 @@
       <c r="B285" t="s">
         <v>7</v>
       </c>
-      <c r="D285" s="2" t="s">
+      <c r="C285" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>242</v>
       </c>
       <c r="E285" t="s">
@@ -7259,7 +8108,10 @@
       <c r="B286" t="s">
         <v>7</v>
       </c>
-      <c r="D286" s="2" t="s">
+      <c r="C286" t="s">
+        <v>7</v>
+      </c>
+      <c r="D286" s="1" t="s">
         <v>243</v>
       </c>
       <c r="E286" t="s">
@@ -7276,7 +8128,10 @@
       <c r="B287" t="s">
         <v>7</v>
       </c>
-      <c r="D287" s="2" t="s">
+      <c r="C287" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>244</v>
       </c>
       <c r="E287" t="s">
@@ -7293,7 +8148,10 @@
       <c r="B288" t="s">
         <v>7</v>
       </c>
-      <c r="D288" s="2" t="s">
+      <c r="C288" t="s">
+        <v>7</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>245</v>
       </c>
       <c r="E288" t="s">
@@ -7310,7 +8168,10 @@
       <c r="B289" t="s">
         <v>7</v>
       </c>
-      <c r="D289" s="2" t="s">
+      <c r="C289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>246</v>
       </c>
       <c r="E289" t="s">
@@ -7327,7 +8188,10 @@
       <c r="B290" t="s">
         <v>7</v>
       </c>
-      <c r="D290" s="2" t="s">
+      <c r="C290" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>247</v>
       </c>
       <c r="E290" t="s">
@@ -7344,7 +8208,10 @@
       <c r="B291" t="s">
         <v>7</v>
       </c>
-      <c r="D291" s="2" t="s">
+      <c r="C291" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>248</v>
       </c>
       <c r="E291" t="s">
@@ -7361,7 +8228,10 @@
       <c r="B292" t="s">
         <v>7</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="C292" t="s">
+        <v>7</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>249</v>
       </c>
       <c r="E292" t="s">
@@ -7378,7 +8248,10 @@
       <c r="B293" t="s">
         <v>7</v>
       </c>
-      <c r="D293" s="2" t="s">
+      <c r="C293" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>250</v>
       </c>
       <c r="E293" t="s">
@@ -7395,7 +8268,10 @@
       <c r="B294" t="s">
         <v>7</v>
       </c>
-      <c r="D294" s="2" t="s">
+      <c r="C294" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>251</v>
       </c>
       <c r="E294" t="s">
@@ -7412,7 +8288,10 @@
       <c r="B295" t="s">
         <v>7</v>
       </c>
-      <c r="D295" s="2" t="s">
+      <c r="C295" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>252</v>
       </c>
       <c r="E295" t="s">
@@ -7429,7 +8308,10 @@
       <c r="B296" t="s">
         <v>7</v>
       </c>
-      <c r="D296" s="2" t="s">
+      <c r="C296" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>253</v>
       </c>
       <c r="E296" t="s">
@@ -7446,7 +8328,10 @@
       <c r="B297" t="s">
         <v>7</v>
       </c>
-      <c r="D297" s="2" t="s">
+      <c r="C297" t="s">
+        <v>7</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>254</v>
       </c>
       <c r="E297" t="s">
@@ -7463,7 +8348,10 @@
       <c r="B298" t="s">
         <v>7</v>
       </c>
-      <c r="D298" s="2" t="s">
+      <c r="C298" t="s">
+        <v>7</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>255</v>
       </c>
       <c r="E298" t="s">
@@ -7480,7 +8368,10 @@
       <c r="B299" t="s">
         <v>7</v>
       </c>
-      <c r="D299" s="2" t="s">
+      <c r="C299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>256</v>
       </c>
       <c r="E299" t="s">
@@ -7497,7 +8388,10 @@
       <c r="B300" t="s">
         <v>7</v>
       </c>
-      <c r="D300" s="2" t="s">
+      <c r="C300" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>257</v>
       </c>
       <c r="E300" t="s">
@@ -7514,7 +8408,10 @@
       <c r="B301" t="s">
         <v>7</v>
       </c>
-      <c r="D301" s="2" t="s">
+      <c r="C301" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>258</v>
       </c>
       <c r="E301" t="s">
@@ -7531,7 +8428,10 @@
       <c r="B302" t="s">
         <v>7</v>
       </c>
-      <c r="D302" s="2" t="s">
+      <c r="C302" t="s">
+        <v>7</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>259</v>
       </c>
       <c r="E302" t="s">
@@ -7548,7 +8448,10 @@
       <c r="B303" t="s">
         <v>7</v>
       </c>
-      <c r="D303" s="2" t="s">
+      <c r="C303" t="s">
+        <v>7</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>260</v>
       </c>
       <c r="E303" t="s">
@@ -7565,7 +8468,10 @@
       <c r="B304" t="s">
         <v>7</v>
       </c>
-      <c r="D304" s="2" t="s">
+      <c r="C304" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>261</v>
       </c>
       <c r="E304" t="s">
@@ -7582,7 +8488,10 @@
       <c r="B305" t="s">
         <v>7</v>
       </c>
-      <c r="D305" s="2" t="s">
+      <c r="C305" t="s">
+        <v>7</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>262</v>
       </c>
       <c r="E305" t="s">
@@ -7599,7 +8508,10 @@
       <c r="B306" t="s">
         <v>7</v>
       </c>
-      <c r="D306" s="2" t="s">
+      <c r="C306" t="s">
+        <v>7</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>263</v>
       </c>
       <c r="E306" t="s">
@@ -7616,7 +8528,10 @@
       <c r="B307" t="s">
         <v>7</v>
       </c>
-      <c r="D307" s="2" t="s">
+      <c r="C307" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>264</v>
       </c>
       <c r="E307" t="s">
@@ -7633,7 +8548,10 @@
       <c r="B308" t="s">
         <v>7</v>
       </c>
-      <c r="D308" s="2" t="s">
+      <c r="C308" t="s">
+        <v>7</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>265</v>
       </c>
       <c r="E308" t="s">
@@ -7650,7 +8568,10 @@
       <c r="B309" t="s">
         <v>7</v>
       </c>
-      <c r="D309" s="2" t="s">
+      <c r="C309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>266</v>
       </c>
       <c r="E309" t="s">
@@ -7667,7 +8588,10 @@
       <c r="B310" t="s">
         <v>7</v>
       </c>
-      <c r="D310" s="2" t="s">
+      <c r="C310" t="s">
+        <v>7</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>267</v>
       </c>
       <c r="E310" t="s">
@@ -7684,7 +8608,10 @@
       <c r="B311" t="s">
         <v>7</v>
       </c>
-      <c r="D311" s="2" t="s">
+      <c r="C311" t="s">
+        <v>7</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>268</v>
       </c>
       <c r="E311" t="s">
@@ -7701,7 +8628,10 @@
       <c r="B312" t="s">
         <v>7</v>
       </c>
-      <c r="D312" s="2" t="s">
+      <c r="C312" t="s">
+        <v>7</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>269</v>
       </c>
       <c r="E312" t="s">
@@ -7718,7 +8648,10 @@
       <c r="B313" t="s">
         <v>7</v>
       </c>
-      <c r="D313" s="2" t="s">
+      <c r="C313" t="s">
+        <v>7</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>270</v>
       </c>
       <c r="E313" t="s">
@@ -7735,7 +8668,10 @@
       <c r="B314" t="s">
         <v>7</v>
       </c>
-      <c r="D314" s="2" t="s">
+      <c r="C314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>271</v>
       </c>
       <c r="E314" t="s">
@@ -7752,7 +8688,10 @@
       <c r="B315" t="s">
         <v>7</v>
       </c>
-      <c r="D315" s="2" t="s">
+      <c r="C315" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>272</v>
       </c>
       <c r="E315" t="s">
@@ -7769,7 +8708,10 @@
       <c r="B316" t="s">
         <v>7</v>
       </c>
-      <c r="D316" s="2" t="s">
+      <c r="C316" t="s">
+        <v>7</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>273</v>
       </c>
       <c r="E316" t="s">
@@ -7786,7 +8728,10 @@
       <c r="B317" t="s">
         <v>7</v>
       </c>
-      <c r="D317" s="2" t="s">
+      <c r="C317" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>274</v>
       </c>
       <c r="E317" t="s">
@@ -7803,7 +8748,10 @@
       <c r="B318" t="s">
         <v>7</v>
       </c>
-      <c r="D318" s="2" t="s">
+      <c r="C318" t="s">
+        <v>7</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>275</v>
       </c>
       <c r="E318" t="s">
@@ -7820,7 +8768,10 @@
       <c r="B319" t="s">
         <v>7</v>
       </c>
-      <c r="D319" s="2" t="s">
+      <c r="C319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>276</v>
       </c>
       <c r="E319" t="s">
@@ -7837,7 +8788,10 @@
       <c r="B320" t="s">
         <v>7</v>
       </c>
-      <c r="D320" s="2" t="s">
+      <c r="C320" t="s">
+        <v>7</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>277</v>
       </c>
       <c r="E320" t="s">
@@ -7854,7 +8808,10 @@
       <c r="B321" t="s">
         <v>7</v>
       </c>
-      <c r="D321" s="2" t="s">
+      <c r="C321" t="s">
+        <v>7</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>278</v>
       </c>
       <c r="E321" t="s">
@@ -7871,7 +8828,10 @@
       <c r="B322" t="s">
         <v>7</v>
       </c>
-      <c r="D322" s="2" t="s">
+      <c r="C322" t="s">
+        <v>7</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>279</v>
       </c>
       <c r="E322" t="s">
@@ -7888,7 +8848,10 @@
       <c r="B323" t="s">
         <v>7</v>
       </c>
-      <c r="D323" s="2" t="s">
+      <c r="C323" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323" s="1" t="s">
         <v>280</v>
       </c>
       <c r="E323" t="s">
@@ -7905,7 +8868,10 @@
       <c r="B324" t="s">
         <v>7</v>
       </c>
-      <c r="D324" s="2" t="s">
+      <c r="C324" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>281</v>
       </c>
       <c r="E324" t="s">
@@ -7922,7 +8888,10 @@
       <c r="B325" t="s">
         <v>7</v>
       </c>
-      <c r="D325" s="2" t="s">
+      <c r="C325" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>282</v>
       </c>
       <c r="E325" t="s">
@@ -7939,7 +8908,10 @@
       <c r="B326" t="s">
         <v>7</v>
       </c>
-      <c r="D326" s="2" t="s">
+      <c r="C326" t="s">
+        <v>7</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>283</v>
       </c>
       <c r="E326" t="s">
@@ -7956,7 +8928,10 @@
       <c r="B327" t="s">
         <v>7</v>
       </c>
-      <c r="D327" s="2" t="s">
+      <c r="C327" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>284</v>
       </c>
       <c r="E327" t="s">
@@ -7973,7 +8948,10 @@
       <c r="B328" t="s">
         <v>7</v>
       </c>
-      <c r="D328" s="2" t="s">
+      <c r="C328" t="s">
+        <v>7</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>285</v>
       </c>
       <c r="E328" t="s">
@@ -7990,7 +8968,10 @@
       <c r="B329" t="s">
         <v>7</v>
       </c>
-      <c r="D329" s="2" t="s">
+      <c r="C329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>286</v>
       </c>
       <c r="E329" t="s">
@@ -8007,7 +8988,10 @@
       <c r="B330" t="s">
         <v>7</v>
       </c>
-      <c r="D330" s="2" t="s">
+      <c r="C330" t="s">
+        <v>7</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>287</v>
       </c>
       <c r="E330" t="s">
@@ -8024,7 +9008,10 @@
       <c r="B331" t="s">
         <v>7</v>
       </c>
-      <c r="D331" s="2" t="s">
+      <c r="C331" t="s">
+        <v>7</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>288</v>
       </c>
       <c r="E331" t="s">
@@ -8041,7 +9028,10 @@
       <c r="B332" t="s">
         <v>7</v>
       </c>
-      <c r="D332" s="2" t="s">
+      <c r="C332" t="s">
+        <v>7</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>289</v>
       </c>
       <c r="E332" t="s">
@@ -8058,7 +9048,10 @@
       <c r="B333" t="s">
         <v>7</v>
       </c>
-      <c r="D333" s="2" t="s">
+      <c r="C333" t="s">
+        <v>7</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>290</v>
       </c>
       <c r="E333" t="s">
@@ -8075,7 +9068,10 @@
       <c r="B334" t="s">
         <v>7</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="C334" t="s">
+        <v>7</v>
+      </c>
+      <c r="D334" s="1" t="s">
         <v>291</v>
       </c>
       <c r="E334" t="s">
@@ -8092,7 +9088,10 @@
       <c r="B335" t="s">
         <v>7</v>
       </c>
-      <c r="D335" s="2" t="s">
+      <c r="C335" t="s">
+        <v>7</v>
+      </c>
+      <c r="D335" s="1" t="s">
         <v>292</v>
       </c>
       <c r="E335" t="s">
@@ -8109,7 +9108,10 @@
       <c r="B336" t="s">
         <v>7</v>
       </c>
-      <c r="D336" s="2" t="s">
+      <c r="C336" t="s">
+        <v>7</v>
+      </c>
+      <c r="D336" s="1" t="s">
         <v>293</v>
       </c>
       <c r="E336" t="s">
@@ -8126,7 +9128,10 @@
       <c r="B337" t="s">
         <v>7</v>
       </c>
-      <c r="D337" s="2" t="s">
+      <c r="C337" t="s">
+        <v>7</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>294</v>
       </c>
       <c r="E337" t="s">
@@ -8143,7 +9148,10 @@
       <c r="B338" t="s">
         <v>7</v>
       </c>
-      <c r="D338" s="2" t="s">
+      <c r="C338" t="s">
+        <v>7</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>295</v>
       </c>
       <c r="E338" t="s">
@@ -8160,7 +9168,10 @@
       <c r="B339" t="s">
         <v>7</v>
       </c>
-      <c r="D339" s="2" t="s">
+      <c r="C339" t="s">
+        <v>7</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>296</v>
       </c>
       <c r="E339" t="s">
@@ -8177,7 +9188,10 @@
       <c r="B340" t="s">
         <v>7</v>
       </c>
-      <c r="D340" s="2" t="s">
+      <c r="C340" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>297</v>
       </c>
       <c r="E340" t="s">
@@ -8194,7 +9208,10 @@
       <c r="B341" t="s">
         <v>7</v>
       </c>
-      <c r="D341" s="2" t="s">
+      <c r="C341" t="s">
+        <v>7</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>298</v>
       </c>
       <c r="E341" t="s">
@@ -8211,7 +9228,10 @@
       <c r="B342" t="s">
         <v>7</v>
       </c>
-      <c r="D342" s="2" t="s">
+      <c r="C342" t="s">
+        <v>7</v>
+      </c>
+      <c r="D342" s="1" t="s">
         <v>299</v>
       </c>
       <c r="E342" t="s">
@@ -8228,7 +9248,10 @@
       <c r="B343" t="s">
         <v>7</v>
       </c>
-      <c r="D343" s="2" t="s">
+      <c r="C343" t="s">
+        <v>7</v>
+      </c>
+      <c r="D343" s="1" t="s">
         <v>300</v>
       </c>
       <c r="E343" t="s">
@@ -8245,7 +9268,10 @@
       <c r="B344" t="s">
         <v>7</v>
       </c>
-      <c r="D344" s="2" t="s">
+      <c r="C344" t="s">
+        <v>7</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E344" t="s">
@@ -8262,7 +9288,10 @@
       <c r="B345" t="s">
         <v>7</v>
       </c>
-      <c r="D345" s="2" t="s">
+      <c r="C345" t="s">
+        <v>7</v>
+      </c>
+      <c r="D345" s="1" t="s">
         <v>302</v>
       </c>
       <c r="E345" t="s">
@@ -8279,7 +9308,10 @@
       <c r="B346" t="s">
         <v>7</v>
       </c>
-      <c r="D346" s="2" t="s">
+      <c r="C346" t="s">
+        <v>7</v>
+      </c>
+      <c r="D346" s="1" t="s">
         <v>303</v>
       </c>
       <c r="E346" t="s">
@@ -8296,7 +9328,10 @@
       <c r="B347" t="s">
         <v>7</v>
       </c>
-      <c r="D347" s="2" t="s">
+      <c r="C347" t="s">
+        <v>7</v>
+      </c>
+      <c r="D347" s="1" t="s">
         <v>304</v>
       </c>
       <c r="E347" t="s">
@@ -8313,7 +9348,10 @@
       <c r="B348" t="s">
         <v>7</v>
       </c>
-      <c r="D348" s="2" t="s">
+      <c r="C348" t="s">
+        <v>7</v>
+      </c>
+      <c r="D348" s="1" t="s">
         <v>305</v>
       </c>
       <c r="E348" t="s">
@@ -8330,7 +9368,10 @@
       <c r="B349" t="s">
         <v>7</v>
       </c>
-      <c r="D349" s="2" t="s">
+      <c r="C349" t="s">
+        <v>7</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E349" t="s">
@@ -8347,7 +9388,10 @@
       <c r="B350" t="s">
         <v>7</v>
       </c>
-      <c r="D350" s="2" t="s">
+      <c r="C350" t="s">
+        <v>7</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>307</v>
       </c>
       <c r="E350" t="s">
@@ -8364,7 +9408,10 @@
       <c r="B351" t="s">
         <v>7</v>
       </c>
-      <c r="D351" s="2" t="s">
+      <c r="C351" t="s">
+        <v>7</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>308</v>
       </c>
       <c r="E351" t="s">
@@ -8381,7 +9428,10 @@
       <c r="B352" t="s">
         <v>7</v>
       </c>
-      <c r="D352" s="2" t="s">
+      <c r="C352" t="s">
+        <v>7</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>309</v>
       </c>
       <c r="E352" t="s">
@@ -8398,7 +9448,10 @@
       <c r="B353" t="s">
         <v>7</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="C353" t="s">
+        <v>7</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>310</v>
       </c>
       <c r="E353" t="s">
@@ -8415,7 +9468,10 @@
       <c r="B354" t="s">
         <v>7</v>
       </c>
-      <c r="D354" s="2" t="s">
+      <c r="C354" t="s">
+        <v>7</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>311</v>
       </c>
       <c r="E354" t="s">
@@ -8432,7 +9488,10 @@
       <c r="B355" t="s">
         <v>7</v>
       </c>
-      <c r="D355" s="2" t="s">
+      <c r="C355" t="s">
+        <v>7</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>312</v>
       </c>
       <c r="E355" t="s">
@@ -8449,7 +9508,10 @@
       <c r="B356" t="s">
         <v>7</v>
       </c>
-      <c r="D356" s="2" t="s">
+      <c r="C356" t="s">
+        <v>7</v>
+      </c>
+      <c r="D356" s="1" t="s">
         <v>313</v>
       </c>
       <c r="E356" t="s">
@@ -8466,7 +9528,10 @@
       <c r="B357" t="s">
         <v>7</v>
       </c>
-      <c r="D357" s="2" t="s">
+      <c r="C357" t="s">
+        <v>7</v>
+      </c>
+      <c r="D357" s="1" t="s">
         <v>314</v>
       </c>
       <c r="E357" t="s">
@@ -8483,7 +9548,10 @@
       <c r="B358" t="s">
         <v>7</v>
       </c>
-      <c r="D358" s="2" t="s">
+      <c r="C358" t="s">
+        <v>7</v>
+      </c>
+      <c r="D358" s="1" t="s">
         <v>315</v>
       </c>
       <c r="E358" t="s">
@@ -8500,7 +9568,10 @@
       <c r="B359" t="s">
         <v>7</v>
       </c>
-      <c r="D359" s="2" t="s">
+      <c r="C359" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" s="1" t="s">
         <v>316</v>
       </c>
       <c r="E359" t="s">
@@ -8517,7 +9588,10 @@
       <c r="B360" t="s">
         <v>7</v>
       </c>
-      <c r="D360" s="2" t="s">
+      <c r="C360" t="s">
+        <v>7</v>
+      </c>
+      <c r="D360" s="1" t="s">
         <v>317</v>
       </c>
       <c r="E360" t="s">
@@ -8534,7 +9608,10 @@
       <c r="B361" t="s">
         <v>7</v>
       </c>
-      <c r="D361" s="2" t="s">
+      <c r="C361" t="s">
+        <v>7</v>
+      </c>
+      <c r="D361" s="1" t="s">
         <v>318</v>
       </c>
       <c r="E361" t="s">
@@ -8551,7 +9628,10 @@
       <c r="B362" t="s">
         <v>7</v>
       </c>
-      <c r="D362" s="2" t="s">
+      <c r="C362" t="s">
+        <v>7</v>
+      </c>
+      <c r="D362" s="1" t="s">
         <v>319</v>
       </c>
       <c r="E362" t="s">
@@ -8568,7 +9648,10 @@
       <c r="B363" t="s">
         <v>7</v>
       </c>
-      <c r="D363" s="2" t="s">
+      <c r="C363" t="s">
+        <v>7</v>
+      </c>
+      <c r="D363" s="1" t="s">
         <v>320</v>
       </c>
       <c r="E363" t="s">
@@ -8585,7 +9668,10 @@
       <c r="B364" t="s">
         <v>7</v>
       </c>
-      <c r="D364" s="2" t="s">
+      <c r="C364" t="s">
+        <v>7</v>
+      </c>
+      <c r="D364" s="1" t="s">
         <v>321</v>
       </c>
       <c r="E364" t="s">
@@ -8602,7 +9688,10 @@
       <c r="B365" t="s">
         <v>7</v>
       </c>
-      <c r="D365" s="2" t="s">
+      <c r="C365" t="s">
+        <v>7</v>
+      </c>
+      <c r="D365" s="1" t="s">
         <v>322</v>
       </c>
       <c r="E365" t="s">
@@ -8619,7 +9708,10 @@
       <c r="B366" t="s">
         <v>7</v>
       </c>
-      <c r="D366" s="2" t="s">
+      <c r="C366" t="s">
+        <v>7</v>
+      </c>
+      <c r="D366" s="1" t="s">
         <v>323</v>
       </c>
       <c r="E366" t="s">
@@ -8636,7 +9728,10 @@
       <c r="B367" t="s">
         <v>7</v>
       </c>
-      <c r="D367" s="2" t="s">
+      <c r="C367" t="s">
+        <v>7</v>
+      </c>
+      <c r="D367" s="1" t="s">
         <v>324</v>
       </c>
       <c r="E367" t="s">
@@ -8653,7 +9748,10 @@
       <c r="B368" t="s">
         <v>7</v>
       </c>
-      <c r="D368" s="2" t="s">
+      <c r="C368" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368" s="1" t="s">
         <v>325</v>
       </c>
       <c r="E368" t="s">
@@ -8670,7 +9768,10 @@
       <c r="B369" t="s">
         <v>7</v>
       </c>
-      <c r="D369" s="2" t="s">
+      <c r="C369" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" s="1" t="s">
         <v>326</v>
       </c>
       <c r="E369" t="s">
@@ -8687,7 +9788,10 @@
       <c r="B370" t="s">
         <v>7</v>
       </c>
-      <c r="D370" s="2" t="s">
+      <c r="C370" t="s">
+        <v>7</v>
+      </c>
+      <c r="D370" s="1" t="s">
         <v>327</v>
       </c>
       <c r="E370" t="s">
@@ -8704,7 +9808,10 @@
       <c r="B371" t="s">
         <v>7</v>
       </c>
-      <c r="D371" s="2" t="s">
+      <c r="C371" t="s">
+        <v>7</v>
+      </c>
+      <c r="D371" s="1" t="s">
         <v>328</v>
       </c>
       <c r="E371" t="s">
@@ -8721,7 +9828,10 @@
       <c r="B372" t="s">
         <v>7</v>
       </c>
-      <c r="D372" s="2" t="s">
+      <c r="C372" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" s="1" t="s">
         <v>329</v>
       </c>
       <c r="E372" t="s">
@@ -8738,7 +9848,10 @@
       <c r="B373" t="s">
         <v>7</v>
       </c>
-      <c r="D373" s="2" t="s">
+      <c r="C373" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" s="1" t="s">
         <v>330</v>
       </c>
       <c r="E373" t="s">
@@ -8755,7 +9868,10 @@
       <c r="B374" t="s">
         <v>7</v>
       </c>
-      <c r="D374" s="2" t="s">
+      <c r="C374" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" s="1" t="s">
         <v>331</v>
       </c>
       <c r="E374" t="s">
@@ -8772,7 +9888,10 @@
       <c r="B375" t="s">
         <v>7</v>
       </c>
-      <c r="D375" s="2" t="s">
+      <c r="C375" t="s">
+        <v>7</v>
+      </c>
+      <c r="D375" s="1" t="s">
         <v>332</v>
       </c>
       <c r="E375" t="s">
@@ -8789,7 +9908,10 @@
       <c r="B376" t="s">
         <v>7</v>
       </c>
-      <c r="D376" s="2" t="s">
+      <c r="C376" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" s="1" t="s">
         <v>333</v>
       </c>
       <c r="E376" t="s">
@@ -8806,7 +9928,10 @@
       <c r="B377" t="s">
         <v>7</v>
       </c>
-      <c r="D377" s="2" t="s">
+      <c r="C377" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" s="1" t="s">
         <v>334</v>
       </c>
       <c r="E377" t="s">
@@ -8823,7 +9948,10 @@
       <c r="B378" t="s">
         <v>7</v>
       </c>
-      <c r="D378" s="2" t="s">
+      <c r="C378" t="s">
+        <v>7</v>
+      </c>
+      <c r="D378" s="1" t="s">
         <v>335</v>
       </c>
       <c r="E378" t="s">
@@ -8840,7 +9968,10 @@
       <c r="B379" t="s">
         <v>7</v>
       </c>
-      <c r="D379" s="2" t="s">
+      <c r="C379" t="s">
+        <v>7</v>
+      </c>
+      <c r="D379" s="1" t="s">
         <v>336</v>
       </c>
       <c r="E379" t="s">
@@ -8857,7 +9988,10 @@
       <c r="B380" t="s">
         <v>7</v>
       </c>
-      <c r="D380" s="2" t="s">
+      <c r="C380" t="s">
+        <v>7</v>
+      </c>
+      <c r="D380" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E380" t="s">
@@ -8874,7 +10008,10 @@
       <c r="B381" t="s">
         <v>7</v>
       </c>
-      <c r="D381" s="2" t="s">
+      <c r="C381" t="s">
+        <v>7</v>
+      </c>
+      <c r="D381" s="1" t="s">
         <v>338</v>
       </c>
       <c r="E381" t="s">
@@ -8891,7 +10028,10 @@
       <c r="B382" t="s">
         <v>7</v>
       </c>
-      <c r="D382" s="2" t="s">
+      <c r="C382" t="s">
+        <v>7</v>
+      </c>
+      <c r="D382" s="1" t="s">
         <v>339</v>
       </c>
       <c r="E382" t="s">
@@ -8908,7 +10048,10 @@
       <c r="B383" t="s">
         <v>7</v>
       </c>
-      <c r="D383" s="2" t="s">
+      <c r="C383" t="s">
+        <v>7</v>
+      </c>
+      <c r="D383" s="1" t="s">
         <v>340</v>
       </c>
       <c r="E383" t="s">
@@ -8925,7 +10068,10 @@
       <c r="B384" t="s">
         <v>7</v>
       </c>
-      <c r="D384" s="2" t="s">
+      <c r="C384" t="s">
+        <v>7</v>
+      </c>
+      <c r="D384" s="1" t="s">
         <v>341</v>
       </c>
       <c r="E384" t="s">
@@ -8942,7 +10088,10 @@
       <c r="B385" t="s">
         <v>7</v>
       </c>
-      <c r="D385" s="2" t="s">
+      <c r="C385" t="s">
+        <v>7</v>
+      </c>
+      <c r="D385" s="1" t="s">
         <v>342</v>
       </c>
       <c r="E385" t="s">
@@ -8959,7 +10108,10 @@
       <c r="B386" t="s">
         <v>7</v>
       </c>
-      <c r="D386" s="2" t="s">
+      <c r="C386" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" s="1" t="s">
         <v>343</v>
       </c>
       <c r="E386" t="s">
@@ -8976,7 +10128,10 @@
       <c r="B387" t="s">
         <v>7</v>
       </c>
-      <c r="D387" s="2" t="s">
+      <c r="C387" t="s">
+        <v>7</v>
+      </c>
+      <c r="D387" s="1" t="s">
         <v>344</v>
       </c>
       <c r="E387" t="s">
@@ -8993,7 +10148,10 @@
       <c r="B388" t="s">
         <v>7</v>
       </c>
-      <c r="D388" s="2" t="s">
+      <c r="C388" t="s">
+        <v>7</v>
+      </c>
+      <c r="D388" s="1" t="s">
         <v>345</v>
       </c>
       <c r="E388" t="s">
@@ -9010,7 +10168,10 @@
       <c r="B389" t="s">
         <v>7</v>
       </c>
-      <c r="D389" s="2" t="s">
+      <c r="C389" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" s="1" t="s">
         <v>346</v>
       </c>
       <c r="E389" t="s">
@@ -9027,7 +10188,10 @@
       <c r="B390" t="s">
         <v>7</v>
       </c>
-      <c r="D390" s="2" t="s">
+      <c r="C390" t="s">
+        <v>7</v>
+      </c>
+      <c r="D390" s="1" t="s">
         <v>347</v>
       </c>
       <c r="E390" t="s">
@@ -9044,7 +10208,10 @@
       <c r="B391" t="s">
         <v>7</v>
       </c>
-      <c r="D391" s="2" t="s">
+      <c r="C391" t="s">
+        <v>7</v>
+      </c>
+      <c r="D391" s="1" t="s">
         <v>348</v>
       </c>
       <c r="E391" t="s">
@@ -9061,7 +10228,10 @@
       <c r="B392" t="s">
         <v>7</v>
       </c>
-      <c r="D392" s="2" t="s">
+      <c r="C392" t="s">
+        <v>7</v>
+      </c>
+      <c r="D392" s="1" t="s">
         <v>349</v>
       </c>
       <c r="E392" t="s">
@@ -9078,7 +10248,10 @@
       <c r="B393" t="s">
         <v>7</v>
       </c>
-      <c r="D393" s="2" t="s">
+      <c r="C393" t="s">
+        <v>7</v>
+      </c>
+      <c r="D393" s="1" t="s">
         <v>350</v>
       </c>
       <c r="E393" t="s">
@@ -9095,7 +10268,10 @@
       <c r="B394" t="s">
         <v>7</v>
       </c>
-      <c r="D394" s="2" t="s">
+      <c r="C394" t="s">
+        <v>7</v>
+      </c>
+      <c r="D394" s="1" t="s">
         <v>351</v>
       </c>
       <c r="E394" t="s">
@@ -9112,7 +10288,10 @@
       <c r="B395" t="s">
         <v>7</v>
       </c>
-      <c r="D395" s="2" t="s">
+      <c r="C395" t="s">
+        <v>7</v>
+      </c>
+      <c r="D395" s="1" t="s">
         <v>352</v>
       </c>
       <c r="E395" t="s">
@@ -9129,7 +10308,10 @@
       <c r="B396" t="s">
         <v>7</v>
       </c>
-      <c r="D396" s="2" t="s">
+      <c r="C396" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396" s="1" t="s">
         <v>353</v>
       </c>
       <c r="E396" t="s">
@@ -9146,7 +10328,10 @@
       <c r="B397" t="s">
         <v>7</v>
       </c>
-      <c r="D397" s="2" t="s">
+      <c r="C397" t="s">
+        <v>7</v>
+      </c>
+      <c r="D397" s="1" t="s">
         <v>354</v>
       </c>
       <c r="E397" t="s">
@@ -9163,7 +10348,10 @@
       <c r="B398" t="s">
         <v>7</v>
       </c>
-      <c r="D398" s="2" t="s">
+      <c r="C398" t="s">
+        <v>7</v>
+      </c>
+      <c r="D398" s="1" t="s">
         <v>355</v>
       </c>
       <c r="E398" t="s">
@@ -9180,7 +10368,10 @@
       <c r="B399" t="s">
         <v>7</v>
       </c>
-      <c r="D399" s="2" t="s">
+      <c r="C399" t="s">
+        <v>7</v>
+      </c>
+      <c r="D399" s="1" t="s">
         <v>356</v>
       </c>
       <c r="E399" t="s">
@@ -9197,7 +10388,10 @@
       <c r="B400" t="s">
         <v>7</v>
       </c>
-      <c r="D400" s="2" t="s">
+      <c r="C400" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" s="1" t="s">
         <v>357</v>
       </c>
       <c r="E400" t="s">
@@ -9214,7 +10408,10 @@
       <c r="B401" t="s">
         <v>7</v>
       </c>
-      <c r="D401" s="2" t="s">
+      <c r="C401" t="s">
+        <v>7</v>
+      </c>
+      <c r="D401" s="1" t="s">
         <v>358</v>
       </c>
       <c r="E401" t="s">
@@ -9231,7 +10428,10 @@
       <c r="B402" t="s">
         <v>7</v>
       </c>
-      <c r="D402" s="2" t="s">
+      <c r="C402" t="s">
+        <v>7</v>
+      </c>
+      <c r="D402" s="1" t="s">
         <v>359</v>
       </c>
       <c r="E402" t="s">
@@ -9248,7 +10448,10 @@
       <c r="B403" t="s">
         <v>7</v>
       </c>
-      <c r="D403" s="2" t="s">
+      <c r="C403" t="s">
+        <v>7</v>
+      </c>
+      <c r="D403" s="1" t="s">
         <v>360</v>
       </c>
       <c r="E403" t="s">
@@ -9265,7 +10468,10 @@
       <c r="B404" t="s">
         <v>7</v>
       </c>
-      <c r="D404" s="2" t="s">
+      <c r="C404" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" s="1" t="s">
         <v>361</v>
       </c>
       <c r="E404" t="s">
@@ -9282,7 +10488,10 @@
       <c r="B405" t="s">
         <v>7</v>
       </c>
-      <c r="D405" s="2" t="s">
+      <c r="C405" t="s">
+        <v>7</v>
+      </c>
+      <c r="D405" s="1" t="s">
         <v>362</v>
       </c>
       <c r="E405" t="s">
@@ -9299,7 +10508,10 @@
       <c r="B406" t="s">
         <v>7</v>
       </c>
-      <c r="D406" s="2" t="s">
+      <c r="C406" t="s">
+        <v>7</v>
+      </c>
+      <c r="D406" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E406" t="s">
@@ -9316,7 +10528,10 @@
       <c r="B407" t="s">
         <v>7</v>
       </c>
-      <c r="D407" s="2" t="s">
+      <c r="C407" t="s">
+        <v>7</v>
+      </c>
+      <c r="D407" s="1" t="s">
         <v>364</v>
       </c>
       <c r="E407" t="s">
@@ -9333,7 +10548,10 @@
       <c r="B408" t="s">
         <v>7</v>
       </c>
-      <c r="D408" s="2" t="s">
+      <c r="C408" t="s">
+        <v>7</v>
+      </c>
+      <c r="D408" s="1" t="s">
         <v>365</v>
       </c>
       <c r="E408" t="s">
@@ -9350,7 +10568,10 @@
       <c r="B409" t="s">
         <v>7</v>
       </c>
-      <c r="D409" s="2" t="s">
+      <c r="C409" t="s">
+        <v>7</v>
+      </c>
+      <c r="D409" s="1" t="s">
         <v>366</v>
       </c>
       <c r="E409" t="s">
@@ -9367,7 +10588,10 @@
       <c r="B410" t="s">
         <v>7</v>
       </c>
-      <c r="D410" s="2" t="s">
+      <c r="C410" t="s">
+        <v>7</v>
+      </c>
+      <c r="D410" s="1" t="s">
         <v>367</v>
       </c>
       <c r="E410" t="s">
@@ -9384,7 +10608,10 @@
       <c r="B411" t="s">
         <v>7</v>
       </c>
-      <c r="D411" s="2" t="s">
+      <c r="C411" t="s">
+        <v>7</v>
+      </c>
+      <c r="D411" s="1" t="s">
         <v>368</v>
       </c>
       <c r="E411" t="s">
@@ -9401,7 +10628,10 @@
       <c r="B412" t="s">
         <v>7</v>
       </c>
-      <c r="D412" s="2" t="s">
+      <c r="C412" t="s">
+        <v>7</v>
+      </c>
+      <c r="D412" s="1" t="s">
         <v>369</v>
       </c>
       <c r="E412" t="s">
@@ -9418,7 +10648,10 @@
       <c r="B413" t="s">
         <v>7</v>
       </c>
-      <c r="D413" s="2" t="s">
+      <c r="C413" t="s">
+        <v>7</v>
+      </c>
+      <c r="D413" s="1" t="s">
         <v>370</v>
       </c>
       <c r="E413" t="s">
@@ -9435,7 +10668,10 @@
       <c r="B414" t="s">
         <v>7</v>
       </c>
-      <c r="D414" s="2" t="s">
+      <c r="C414" t="s">
+        <v>7</v>
+      </c>
+      <c r="D414" s="1" t="s">
         <v>371</v>
       </c>
       <c r="E414" t="s">
@@ -9452,7 +10688,10 @@
       <c r="B415" t="s">
         <v>7</v>
       </c>
-      <c r="D415" s="2" t="s">
+      <c r="C415" t="s">
+        <v>7</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>372</v>
       </c>
       <c r="E415" t="s">
@@ -9469,7 +10708,10 @@
       <c r="B416" t="s">
         <v>7</v>
       </c>
-      <c r="D416" s="2" t="s">
+      <c r="C416" t="s">
+        <v>7</v>
+      </c>
+      <c r="D416" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E416" t="s">
@@ -9486,7 +10728,10 @@
       <c r="B417" t="s">
         <v>7</v>
       </c>
-      <c r="D417" s="2" t="s">
+      <c r="C417" t="s">
+        <v>7</v>
+      </c>
+      <c r="D417" s="1" t="s">
         <v>374</v>
       </c>
       <c r="E417" t="s">
@@ -9503,7 +10748,10 @@
       <c r="B418" t="s">
         <v>7</v>
       </c>
-      <c r="D418" s="2" t="s">
+      <c r="C418" t="s">
+        <v>7</v>
+      </c>
+      <c r="D418" s="1" t="s">
         <v>375</v>
       </c>
       <c r="E418" t="s">
@@ -9520,7 +10768,10 @@
       <c r="B419" t="s">
         <v>7</v>
       </c>
-      <c r="D419" s="2" t="s">
+      <c r="C419" t="s">
+        <v>7</v>
+      </c>
+      <c r="D419" s="1" t="s">
         <v>376</v>
       </c>
       <c r="E419" t="s">
@@ -9537,7 +10788,10 @@
       <c r="B420" t="s">
         <v>7</v>
       </c>
-      <c r="D420" s="2" t="s">
+      <c r="C420" t="s">
+        <v>7</v>
+      </c>
+      <c r="D420" s="1" t="s">
         <v>377</v>
       </c>
       <c r="E420" t="s">
@@ -9554,7 +10808,10 @@
       <c r="B421" t="s">
         <v>7</v>
       </c>
-      <c r="D421" s="2" t="s">
+      <c r="C421" t="s">
+        <v>7</v>
+      </c>
+      <c r="D421" s="1" t="s">
         <v>378</v>
       </c>
       <c r="E421" t="s">
@@ -9571,7 +10828,10 @@
       <c r="B422" t="s">
         <v>7</v>
       </c>
-      <c r="D422" s="2" t="s">
+      <c r="C422" t="s">
+        <v>7</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>379</v>
       </c>
       <c r="E422" t="s">
@@ -9588,7 +10848,10 @@
       <c r="B423" t="s">
         <v>7</v>
       </c>
-      <c r="D423" s="2" t="s">
+      <c r="C423" t="s">
+        <v>7</v>
+      </c>
+      <c r="D423" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E423" t="s">
@@ -9605,7 +10868,10 @@
       <c r="B424" t="s">
         <v>7</v>
       </c>
-      <c r="D424" s="2" t="s">
+      <c r="C424" t="s">
+        <v>7</v>
+      </c>
+      <c r="D424" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E424" t="s">
@@ -9622,7 +10888,10 @@
       <c r="B425" t="s">
         <v>7</v>
       </c>
-      <c r="D425" s="2" t="s">
+      <c r="C425" t="s">
+        <v>7</v>
+      </c>
+      <c r="D425" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E425" t="s">
@@ -9639,7 +10908,10 @@
       <c r="B426" t="s">
         <v>7</v>
       </c>
-      <c r="D426" s="2" t="s">
+      <c r="C426" t="s">
+        <v>7</v>
+      </c>
+      <c r="D426" s="1" t="s">
         <v>383</v>
       </c>
       <c r="E426" t="s">
@@ -9656,7 +10928,10 @@
       <c r="B427" t="s">
         <v>7</v>
       </c>
-      <c r="D427" s="2" t="s">
+      <c r="C427" t="s">
+        <v>7</v>
+      </c>
+      <c r="D427" s="1" t="s">
         <v>384</v>
       </c>
       <c r="E427" t="s">
@@ -9673,7 +10948,10 @@
       <c r="B428" t="s">
         <v>7</v>
       </c>
-      <c r="D428" s="2" t="s">
+      <c r="C428" t="s">
+        <v>7</v>
+      </c>
+      <c r="D428" s="1" t="s">
         <v>385</v>
       </c>
       <c r="E428" t="s">
@@ -9690,7 +10968,10 @@
       <c r="B429" t="s">
         <v>7</v>
       </c>
-      <c r="D429" s="2" t="s">
+      <c r="C429" t="s">
+        <v>7</v>
+      </c>
+      <c r="D429" s="1" t="s">
         <v>386</v>
       </c>
       <c r="E429" t="s">
@@ -9707,7 +10988,10 @@
       <c r="B430" t="s">
         <v>7</v>
       </c>
-      <c r="D430" s="2" t="s">
+      <c r="C430" t="s">
+        <v>7</v>
+      </c>
+      <c r="D430" s="1" t="s">
         <v>387</v>
       </c>
       <c r="E430" t="s">
@@ -9724,7 +11008,10 @@
       <c r="B431" t="s">
         <v>7</v>
       </c>
-      <c r="D431" s="2" t="s">
+      <c r="C431" t="s">
+        <v>7</v>
+      </c>
+      <c r="D431" s="1" t="s">
         <v>388</v>
       </c>
       <c r="E431" t="s">
@@ -9741,7 +11028,10 @@
       <c r="B432" t="s">
         <v>7</v>
       </c>
-      <c r="D432" s="2" t="s">
+      <c r="C432" t="s">
+        <v>7</v>
+      </c>
+      <c r="D432" s="1" t="s">
         <v>389</v>
       </c>
       <c r="E432" t="s">
@@ -9758,7 +11048,10 @@
       <c r="B433" t="s">
         <v>7</v>
       </c>
-      <c r="D433" s="2" t="s">
+      <c r="C433" t="s">
+        <v>7</v>
+      </c>
+      <c r="D433" s="1" t="s">
         <v>390</v>
       </c>
       <c r="E433" t="s">
@@ -9775,7 +11068,10 @@
       <c r="B434" t="s">
         <v>7</v>
       </c>
-      <c r="D434" s="2" t="s">
+      <c r="C434" t="s">
+        <v>7</v>
+      </c>
+      <c r="D434" s="1" t="s">
         <v>391</v>
       </c>
       <c r="E434" t="s">
@@ -9792,7 +11088,10 @@
       <c r="B435" t="s">
         <v>7</v>
       </c>
-      <c r="D435" s="2" t="s">
+      <c r="C435" t="s">
+        <v>7</v>
+      </c>
+      <c r="D435" s="1" t="s">
         <v>392</v>
       </c>
       <c r="E435" t="s">
@@ -9809,7 +11108,10 @@
       <c r="B436" t="s">
         <v>7</v>
       </c>
-      <c r="D436" s="2" t="s">
+      <c r="C436" t="s">
+        <v>7</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E436" t="s">
@@ -9826,7 +11128,10 @@
       <c r="B437" t="s">
         <v>7</v>
       </c>
-      <c r="D437" s="2" t="s">
+      <c r="C437" t="s">
+        <v>7</v>
+      </c>
+      <c r="D437" s="1" t="s">
         <v>394</v>
       </c>
       <c r="E437" t="s">
@@ -9843,7 +11148,10 @@
       <c r="B438" t="s">
         <v>7</v>
       </c>
-      <c r="D438" s="2" t="s">
+      <c r="C438" t="s">
+        <v>7</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>395</v>
       </c>
       <c r="E438" t="s">
@@ -9860,7 +11168,10 @@
       <c r="B439" t="s">
         <v>7</v>
       </c>
-      <c r="D439" s="2" t="s">
+      <c r="C439" t="s">
+        <v>7</v>
+      </c>
+      <c r="D439" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E439" t="s">
@@ -9877,7 +11188,10 @@
       <c r="B440" t="s">
         <v>7</v>
       </c>
-      <c r="D440" s="2" t="s">
+      <c r="C440" t="s">
+        <v>7</v>
+      </c>
+      <c r="D440" s="1" t="s">
         <v>397</v>
       </c>
       <c r="E440" t="s">
@@ -9894,7 +11208,10 @@
       <c r="B441" t="s">
         <v>7</v>
       </c>
-      <c r="D441" s="2" t="s">
+      <c r="C441" t="s">
+        <v>7</v>
+      </c>
+      <c r="D441" s="1" t="s">
         <v>398</v>
       </c>
       <c r="E441" t="s">
@@ -9911,7 +11228,10 @@
       <c r="B442" t="s">
         <v>7</v>
       </c>
-      <c r="D442" s="2" t="s">
+      <c r="C442" t="s">
+        <v>7</v>
+      </c>
+      <c r="D442" s="1" t="s">
         <v>399</v>
       </c>
       <c r="E442" t="s">
@@ -9928,7 +11248,10 @@
       <c r="B443" t="s">
         <v>7</v>
       </c>
-      <c r="D443" s="2" t="s">
+      <c r="C443" t="s">
+        <v>7</v>
+      </c>
+      <c r="D443" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E443" t="s">
@@ -9945,7 +11268,10 @@
       <c r="B444" t="s">
         <v>7</v>
       </c>
-      <c r="D444" s="2" t="s">
+      <c r="C444" t="s">
+        <v>7</v>
+      </c>
+      <c r="D444" s="1" t="s">
         <v>401</v>
       </c>
       <c r="E444" t="s">
@@ -9962,7 +11288,10 @@
       <c r="B445" t="s">
         <v>7</v>
       </c>
-      <c r="D445" s="2" t="s">
+      <c r="C445" t="s">
+        <v>7</v>
+      </c>
+      <c r="D445" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E445" t="s">
@@ -9979,7 +11308,10 @@
       <c r="B446" t="s">
         <v>7</v>
       </c>
-      <c r="D446" s="2" t="s">
+      <c r="C446" t="s">
+        <v>7</v>
+      </c>
+      <c r="D446" s="1" t="s">
         <v>403</v>
       </c>
       <c r="E446" t="s">
@@ -9996,7 +11328,10 @@
       <c r="B447" t="s">
         <v>7</v>
       </c>
-      <c r="D447" s="2" t="s">
+      <c r="C447" t="s">
+        <v>7</v>
+      </c>
+      <c r="D447" s="1" t="s">
         <v>404</v>
       </c>
       <c r="E447" t="s">
@@ -10013,7 +11348,10 @@
       <c r="B448" t="s">
         <v>7</v>
       </c>
-      <c r="D448" s="2" t="s">
+      <c r="C448" t="s">
+        <v>7</v>
+      </c>
+      <c r="D448" s="1" t="s">
         <v>405</v>
       </c>
       <c r="E448" t="s">
@@ -10030,7 +11368,10 @@
       <c r="B449" t="s">
         <v>7</v>
       </c>
-      <c r="D449" s="2" t="s">
+      <c r="C449" t="s">
+        <v>7</v>
+      </c>
+      <c r="D449" s="1" t="s">
         <v>406</v>
       </c>
       <c r="E449" t="s">
@@ -10047,7 +11388,10 @@
       <c r="B450" t="s">
         <v>7</v>
       </c>
-      <c r="D450" s="2" t="s">
+      <c r="C450" t="s">
+        <v>7</v>
+      </c>
+      <c r="D450" s="1" t="s">
         <v>407</v>
       </c>
       <c r="E450" t="s">
@@ -10064,7 +11408,10 @@
       <c r="B451" t="s">
         <v>7</v>
       </c>
-      <c r="D451" s="2" t="s">
+      <c r="C451" t="s">
+        <v>7</v>
+      </c>
+      <c r="D451" s="1" t="s">
         <v>408</v>
       </c>
       <c r="E451" t="s">
@@ -10081,7 +11428,10 @@
       <c r="B452" t="s">
         <v>7</v>
       </c>
-      <c r="D452" s="2" t="s">
+      <c r="C452" t="s">
+        <v>7</v>
+      </c>
+      <c r="D452" s="1" t="s">
         <v>409</v>
       </c>
       <c r="E452" t="s">
@@ -10098,7 +11448,10 @@
       <c r="B453" t="s">
         <v>7</v>
       </c>
-      <c r="D453" s="2" t="s">
+      <c r="C453" t="s">
+        <v>7</v>
+      </c>
+      <c r="D453" s="1" t="s">
         <v>410</v>
       </c>
       <c r="E453" t="s">
@@ -10115,7 +11468,10 @@
       <c r="B454" t="s">
         <v>7</v>
       </c>
-      <c r="D454" s="2" t="s">
+      <c r="C454" t="s">
+        <v>7</v>
+      </c>
+      <c r="D454" s="1" t="s">
         <v>411</v>
       </c>
       <c r="E454" t="s">
@@ -10132,7 +11488,10 @@
       <c r="B455" t="s">
         <v>7</v>
       </c>
-      <c r="D455" s="2" t="s">
+      <c r="C455" t="s">
+        <v>7</v>
+      </c>
+      <c r="D455" s="1" t="s">
         <v>412</v>
       </c>
       <c r="E455" t="s">
@@ -10149,7 +11508,10 @@
       <c r="B456" t="s">
         <v>7</v>
       </c>
-      <c r="D456" s="2" t="s">
+      <c r="C456" t="s">
+        <v>7</v>
+      </c>
+      <c r="D456" s="1" t="s">
         <v>413</v>
       </c>
       <c r="E456" t="s">
@@ -10166,7 +11528,10 @@
       <c r="B457" t="s">
         <v>7</v>
       </c>
-      <c r="D457" s="2" t="s">
+      <c r="C457" t="s">
+        <v>7</v>
+      </c>
+      <c r="D457" s="1" t="s">
         <v>414</v>
       </c>
       <c r="E457" t="s">
@@ -10183,7 +11548,10 @@
       <c r="B458" t="s">
         <v>7</v>
       </c>
-      <c r="D458" s="2" t="s">
+      <c r="C458" t="s">
+        <v>7</v>
+      </c>
+      <c r="D458" s="1" t="s">
         <v>415</v>
       </c>
       <c r="E458" t="s">
@@ -10200,7 +11568,10 @@
       <c r="B459" t="s">
         <v>7</v>
       </c>
-      <c r="D459" s="2" t="s">
+      <c r="C459" t="s">
+        <v>7</v>
+      </c>
+      <c r="D459" s="1" t="s">
         <v>416</v>
       </c>
       <c r="E459" t="s">
@@ -10217,7 +11588,10 @@
       <c r="B460" t="s">
         <v>7</v>
       </c>
-      <c r="D460" s="2" t="s">
+      <c r="C460" t="s">
+        <v>7</v>
+      </c>
+      <c r="D460" s="1" t="s">
         <v>417</v>
       </c>
       <c r="E460" t="s">
@@ -10234,7 +11608,10 @@
       <c r="B461" t="s">
         <v>7</v>
       </c>
-      <c r="D461" s="2" t="s">
+      <c r="C461" t="s">
+        <v>7</v>
+      </c>
+      <c r="D461" s="1" t="s">
         <v>418</v>
       </c>
       <c r="E461" t="s">
@@ -10251,7 +11628,10 @@
       <c r="B462" t="s">
         <v>7</v>
       </c>
-      <c r="D462" s="2" t="s">
+      <c r="C462" t="s">
+        <v>7</v>
+      </c>
+      <c r="D462" s="1" t="s">
         <v>419</v>
       </c>
       <c r="E462" t="s">
@@ -10268,7 +11648,10 @@
       <c r="B463" t="s">
         <v>7</v>
       </c>
-      <c r="D463" s="2" t="s">
+      <c r="C463" t="s">
+        <v>7</v>
+      </c>
+      <c r="D463" s="1" t="s">
         <v>420</v>
       </c>
       <c r="E463" t="s">
@@ -10285,7 +11668,10 @@
       <c r="B464" t="s">
         <v>7</v>
       </c>
-      <c r="D464" s="2" t="s">
+      <c r="C464" t="s">
+        <v>7</v>
+      </c>
+      <c r="D464" s="1" t="s">
         <v>421</v>
       </c>
       <c r="E464" t="s">
@@ -10302,7 +11688,10 @@
       <c r="B465" t="s">
         <v>7</v>
       </c>
-      <c r="D465" s="2" t="s">
+      <c r="C465" t="s">
+        <v>7</v>
+      </c>
+      <c r="D465" s="1" t="s">
         <v>422</v>
       </c>
       <c r="E465" t="s">
@@ -10319,7 +11708,10 @@
       <c r="B466" t="s">
         <v>7</v>
       </c>
-      <c r="D466" s="2" t="s">
+      <c r="C466" t="s">
+        <v>7</v>
+      </c>
+      <c r="D466" s="1" t="s">
         <v>423</v>
       </c>
       <c r="E466" t="s">
@@ -10336,7 +11728,10 @@
       <c r="B467" t="s">
         <v>7</v>
       </c>
-      <c r="D467" s="2" t="s">
+      <c r="C467" t="s">
+        <v>7</v>
+      </c>
+      <c r="D467" s="1" t="s">
         <v>424</v>
       </c>
       <c r="E467" t="s">
@@ -10353,7 +11748,10 @@
       <c r="B468" t="s">
         <v>7</v>
       </c>
-      <c r="D468" s="2" t="s">
+      <c r="C468" t="s">
+        <v>7</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>425</v>
       </c>
       <c r="E468" t="s">
@@ -10370,7 +11768,10 @@
       <c r="B469" t="s">
         <v>7</v>
       </c>
-      <c r="D469" s="2" t="s">
+      <c r="C469" t="s">
+        <v>7</v>
+      </c>
+      <c r="D469" s="1" t="s">
         <v>426</v>
       </c>
       <c r="E469" t="s">
@@ -10387,7 +11788,10 @@
       <c r="B470" t="s">
         <v>7</v>
       </c>
-      <c r="D470" s="2" t="s">
+      <c r="C470" t="s">
+        <v>7</v>
+      </c>
+      <c r="D470" s="1" t="s">
         <v>427</v>
       </c>
       <c r="E470" t="s">
@@ -10404,7 +11808,10 @@
       <c r="B471" t="s">
         <v>7</v>
       </c>
-      <c r="D471" s="2" t="s">
+      <c r="C471" t="s">
+        <v>7</v>
+      </c>
+      <c r="D471" s="1" t="s">
         <v>428</v>
       </c>
       <c r="E471" t="s">
@@ -10421,7 +11828,10 @@
       <c r="B472" t="s">
         <v>7</v>
       </c>
-      <c r="D472" s="2" t="s">
+      <c r="C472" t="s">
+        <v>7</v>
+      </c>
+      <c r="D472" s="1" t="s">
         <v>429</v>
       </c>
       <c r="E472" t="s">
@@ -10438,7 +11848,10 @@
       <c r="B473" t="s">
         <v>7</v>
       </c>
-      <c r="D473" s="2" t="s">
+      <c r="C473" t="s">
+        <v>7</v>
+      </c>
+      <c r="D473" s="1" t="s">
         <v>430</v>
       </c>
       <c r="E473" t="s">
@@ -10455,7 +11868,10 @@
       <c r="B474" t="s">
         <v>7</v>
       </c>
-      <c r="D474" s="2" t="s">
+      <c r="C474" t="s">
+        <v>7</v>
+      </c>
+      <c r="D474" s="1" t="s">
         <v>431</v>
       </c>
       <c r="E474" t="s">
@@ -10472,7 +11888,10 @@
       <c r="B475" t="s">
         <v>7</v>
       </c>
-      <c r="D475" s="2" t="s">
+      <c r="C475" t="s">
+        <v>7</v>
+      </c>
+      <c r="D475" s="1" t="s">
         <v>432</v>
       </c>
       <c r="E475" t="s">
@@ -10489,7 +11908,10 @@
       <c r="B476" t="s">
         <v>7</v>
       </c>
-      <c r="D476" s="2" t="s">
+      <c r="C476" t="s">
+        <v>7</v>
+      </c>
+      <c r="D476" s="1" t="s">
         <v>433</v>
       </c>
       <c r="E476" t="s">
@@ -10506,7 +11928,10 @@
       <c r="B477" t="s">
         <v>7</v>
       </c>
-      <c r="D477" s="2" t="s">
+      <c r="C477" t="s">
+        <v>7</v>
+      </c>
+      <c r="D477" s="1" t="s">
         <v>434</v>
       </c>
       <c r="E477" t="s">
@@ -10523,7 +11948,10 @@
       <c r="B478" t="s">
         <v>7</v>
       </c>
-      <c r="D478" s="2" t="s">
+      <c r="C478" t="s">
+        <v>7</v>
+      </c>
+      <c r="D478" s="1" t="s">
         <v>435</v>
       </c>
       <c r="E478" t="s">
@@ -10540,7 +11968,10 @@
       <c r="B479" t="s">
         <v>7</v>
       </c>
-      <c r="D479" s="2" t="s">
+      <c r="C479" t="s">
+        <v>7</v>
+      </c>
+      <c r="D479" s="1" t="s">
         <v>436</v>
       </c>
       <c r="E479" t="s">
@@ -10557,7 +11988,10 @@
       <c r="B480" t="s">
         <v>7</v>
       </c>
-      <c r="D480" s="2" t="s">
+      <c r="C480" t="s">
+        <v>7</v>
+      </c>
+      <c r="D480" s="1" t="s">
         <v>437</v>
       </c>
       <c r="E480" t="s">
@@ -10574,7 +12008,10 @@
       <c r="B481" t="s">
         <v>7</v>
       </c>
-      <c r="D481" s="2" t="s">
+      <c r="C481" t="s">
+        <v>7</v>
+      </c>
+      <c r="D481" s="1" t="s">
         <v>438</v>
       </c>
       <c r="E481" t="s">
@@ -10591,7 +12028,10 @@
       <c r="B482" t="s">
         <v>7</v>
       </c>
-      <c r="D482" s="2" t="s">
+      <c r="C482" t="s">
+        <v>7</v>
+      </c>
+      <c r="D482" s="1" t="s">
         <v>439</v>
       </c>
       <c r="E482" t="s">
@@ -10608,7 +12048,10 @@
       <c r="B483" t="s">
         <v>7</v>
       </c>
-      <c r="D483" s="2" t="s">
+      <c r="C483" t="s">
+        <v>7</v>
+      </c>
+      <c r="D483" s="1" t="s">
         <v>440</v>
       </c>
       <c r="E483" t="s">
@@ -10625,7 +12068,10 @@
       <c r="B484" t="s">
         <v>7</v>
       </c>
-      <c r="D484" s="2" t="s">
+      <c r="C484" t="s">
+        <v>7</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>441</v>
       </c>
       <c r="E484" t="s">
@@ -10642,7 +12088,10 @@
       <c r="B485" t="s">
         <v>7</v>
       </c>
-      <c r="D485" s="2" t="s">
+      <c r="C485" t="s">
+        <v>7</v>
+      </c>
+      <c r="D485" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E485" t="s">
@@ -10659,7 +12108,10 @@
       <c r="B486" t="s">
         <v>7</v>
       </c>
-      <c r="D486" s="2" t="s">
+      <c r="C486" t="s">
+        <v>7</v>
+      </c>
+      <c r="D486" s="1" t="s">
         <v>443</v>
       </c>
       <c r="E486" t="s">
@@ -10676,7 +12128,10 @@
       <c r="B487" t="s">
         <v>7</v>
       </c>
-      <c r="D487" s="2" t="s">
+      <c r="C487" t="s">
+        <v>7</v>
+      </c>
+      <c r="D487" s="1" t="s">
         <v>444</v>
       </c>
       <c r="E487" t="s">
@@ -10693,7 +12148,10 @@
       <c r="B488" t="s">
         <v>7</v>
       </c>
-      <c r="D488" s="2" t="s">
+      <c r="C488" t="s">
+        <v>7</v>
+      </c>
+      <c r="D488" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E488" t="s">
@@ -10710,7 +12168,10 @@
       <c r="B489" t="s">
         <v>7</v>
       </c>
-      <c r="D489" s="2" t="s">
+      <c r="C489" t="s">
+        <v>7</v>
+      </c>
+      <c r="D489" s="1" t="s">
         <v>446</v>
       </c>
       <c r="E489" t="s">
@@ -10727,7 +12188,10 @@
       <c r="B490" t="s">
         <v>7</v>
       </c>
-      <c r="D490" s="2" t="s">
+      <c r="C490" t="s">
+        <v>7</v>
+      </c>
+      <c r="D490" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E490" t="s">
@@ -10744,7 +12208,10 @@
       <c r="B491" t="s">
         <v>7</v>
       </c>
-      <c r="D491" s="2" t="s">
+      <c r="C491" t="s">
+        <v>7</v>
+      </c>
+      <c r="D491" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E491" t="s">
@@ -10761,7 +12228,10 @@
       <c r="B492" t="s">
         <v>7</v>
       </c>
-      <c r="D492" s="2" t="s">
+      <c r="C492" t="s">
+        <v>7</v>
+      </c>
+      <c r="D492" s="1" t="s">
         <v>449</v>
       </c>
       <c r="E492" t="s">
@@ -10778,7 +12248,10 @@
       <c r="B493" t="s">
         <v>7</v>
       </c>
-      <c r="D493" s="2" t="s">
+      <c r="C493" t="s">
+        <v>7</v>
+      </c>
+      <c r="D493" s="1" t="s">
         <v>450</v>
       </c>
       <c r="E493" t="s">
@@ -10795,7 +12268,10 @@
       <c r="B494" t="s">
         <v>7</v>
       </c>
-      <c r="D494" s="2" t="s">
+      <c r="C494" t="s">
+        <v>7</v>
+      </c>
+      <c r="D494" s="1" t="s">
         <v>451</v>
       </c>
       <c r="E494" t="s">
@@ -10812,7 +12288,10 @@
       <c r="B495" t="s">
         <v>7</v>
       </c>
-      <c r="D495" s="2" t="s">
+      <c r="C495" t="s">
+        <v>7</v>
+      </c>
+      <c r="D495" s="1" t="s">
         <v>452</v>
       </c>
       <c r="E495" t="s">
@@ -10829,7 +12308,10 @@
       <c r="B496" t="s">
         <v>7</v>
       </c>
-      <c r="D496" s="2" t="s">
+      <c r="C496" t="s">
+        <v>7</v>
+      </c>
+      <c r="D496" s="1" t="s">
         <v>453</v>
       </c>
       <c r="E496" t="s">
@@ -10846,7 +12328,10 @@
       <c r="B497" t="s">
         <v>7</v>
       </c>
-      <c r="D497" s="2" t="s">
+      <c r="C497" t="s">
+        <v>7</v>
+      </c>
+      <c r="D497" s="1" t="s">
         <v>454</v>
       </c>
       <c r="E497" t="s">
@@ -10863,7 +12348,10 @@
       <c r="B498" t="s">
         <v>7</v>
       </c>
-      <c r="D498" s="2" t="s">
+      <c r="C498" t="s">
+        <v>7</v>
+      </c>
+      <c r="D498" s="1" t="s">
         <v>455</v>
       </c>
       <c r="E498" t="s">
@@ -10880,7 +12368,10 @@
       <c r="B499" t="s">
         <v>7</v>
       </c>
-      <c r="D499" s="2" t="s">
+      <c r="C499" t="s">
+        <v>7</v>
+      </c>
+      <c r="D499" s="1" t="s">
         <v>456</v>
       </c>
       <c r="E499" t="s">
@@ -10897,7 +12388,10 @@
       <c r="B500" t="s">
         <v>7</v>
       </c>
-      <c r="D500" s="2" t="s">
+      <c r="C500" t="s">
+        <v>7</v>
+      </c>
+      <c r="D500" s="1" t="s">
         <v>457</v>
       </c>
       <c r="E500" t="s">
@@ -10914,7 +12408,10 @@
       <c r="B501" t="s">
         <v>7</v>
       </c>
-      <c r="D501" s="2" t="s">
+      <c r="C501" t="s">
+        <v>7</v>
+      </c>
+      <c r="D501" s="1" t="s">
         <v>458</v>
       </c>
       <c r="E501" t="s">
@@ -10931,7 +12428,10 @@
       <c r="B502" t="s">
         <v>7</v>
       </c>
-      <c r="D502" s="2" t="s">
+      <c r="C502" t="s">
+        <v>7</v>
+      </c>
+      <c r="D502" s="1" t="s">
         <v>459</v>
       </c>
       <c r="E502" t="s">
@@ -10948,7 +12448,10 @@
       <c r="B503" t="s">
         <v>7</v>
       </c>
-      <c r="D503" s="2" t="s">
+      <c r="C503" t="s">
+        <v>7</v>
+      </c>
+      <c r="D503" s="1" t="s">
         <v>460</v>
       </c>
       <c r="E503" t="s">
@@ -10965,7 +12468,10 @@
       <c r="B504" t="s">
         <v>7</v>
       </c>
-      <c r="D504" s="2" t="s">
+      <c r="C504" t="s">
+        <v>7</v>
+      </c>
+      <c r="D504" s="1" t="s">
         <v>461</v>
       </c>
       <c r="E504" t="s">
@@ -10982,7 +12488,10 @@
       <c r="B505" t="s">
         <v>7</v>
       </c>
-      <c r="D505" s="2" t="s">
+      <c r="C505" t="s">
+        <v>7</v>
+      </c>
+      <c r="D505" s="1" t="s">
         <v>462</v>
       </c>
       <c r="E505" t="s">
@@ -10999,7 +12508,10 @@
       <c r="B506" t="s">
         <v>7</v>
       </c>
-      <c r="D506" s="2" t="s">
+      <c r="C506" t="s">
+        <v>7</v>
+      </c>
+      <c r="D506" s="1" t="s">
         <v>463</v>
       </c>
       <c r="E506" t="s">
@@ -11016,7 +12528,10 @@
       <c r="B507" t="s">
         <v>7</v>
       </c>
-      <c r="D507" s="2" t="s">
+      <c r="C507" t="s">
+        <v>7</v>
+      </c>
+      <c r="D507" s="1" t="s">
         <v>464</v>
       </c>
       <c r="E507" t="s">
@@ -11033,7 +12548,10 @@
       <c r="B508" t="s">
         <v>7</v>
       </c>
-      <c r="D508" s="2" t="s">
+      <c r="C508" t="s">
+        <v>7</v>
+      </c>
+      <c r="D508" s="1" t="s">
         <v>465</v>
       </c>
       <c r="E508" t="s">
@@ -11050,7 +12568,10 @@
       <c r="B509" t="s">
         <v>7</v>
       </c>
-      <c r="D509" s="2" t="s">
+      <c r="C509" t="s">
+        <v>7</v>
+      </c>
+      <c r="D509" s="1" t="s">
         <v>466</v>
       </c>
       <c r="E509" t="s">
@@ -11067,7 +12588,10 @@
       <c r="B510" t="s">
         <v>7</v>
       </c>
-      <c r="D510" s="2" t="s">
+      <c r="C510" t="s">
+        <v>7</v>
+      </c>
+      <c r="D510" s="1" t="s">
         <v>467</v>
       </c>
       <c r="E510" t="s">
@@ -11084,7 +12608,10 @@
       <c r="B511" t="s">
         <v>7</v>
       </c>
-      <c r="D511" s="2" t="s">
+      <c r="C511" t="s">
+        <v>7</v>
+      </c>
+      <c r="D511" s="1" t="s">
         <v>468</v>
       </c>
       <c r="E511" t="s">
@@ -11101,7 +12628,10 @@
       <c r="B512" t="s">
         <v>7</v>
       </c>
-      <c r="D512" s="2" t="s">
+      <c r="C512" t="s">
+        <v>7</v>
+      </c>
+      <c r="D512" s="1" t="s">
         <v>469</v>
       </c>
       <c r="E512" t="s">
@@ -11118,7 +12648,10 @@
       <c r="B513" t="s">
         <v>7</v>
       </c>
-      <c r="D513" s="2" t="s">
+      <c r="C513" t="s">
+        <v>7</v>
+      </c>
+      <c r="D513" s="1" t="s">
         <v>470</v>
       </c>
       <c r="E513" t="s">
@@ -11135,7 +12668,10 @@
       <c r="B514" t="s">
         <v>7</v>
       </c>
-      <c r="D514" s="2" t="s">
+      <c r="C514" t="s">
+        <v>7</v>
+      </c>
+      <c r="D514" s="1" t="s">
         <v>471</v>
       </c>
       <c r="E514" t="s">
@@ -11152,7 +12688,10 @@
       <c r="B515" t="s">
         <v>7</v>
       </c>
-      <c r="D515" s="2" t="s">
+      <c r="C515" t="s">
+        <v>7</v>
+      </c>
+      <c r="D515" s="1" t="s">
         <v>472</v>
       </c>
       <c r="E515" t="s">
@@ -11169,7 +12708,10 @@
       <c r="B516" t="s">
         <v>7</v>
       </c>
-      <c r="D516" s="2" t="s">
+      <c r="C516" t="s">
+        <v>7</v>
+      </c>
+      <c r="D516" s="1" t="s">
         <v>473</v>
       </c>
       <c r="E516" t="s">
@@ -11186,7 +12728,10 @@
       <c r="B517" t="s">
         <v>7</v>
       </c>
-      <c r="D517" s="2" t="s">
+      <c r="C517" t="s">
+        <v>7</v>
+      </c>
+      <c r="D517" s="1" t="s">
         <v>474</v>
       </c>
       <c r="E517" t="s">
@@ -11203,7 +12748,10 @@
       <c r="B518" t="s">
         <v>7</v>
       </c>
-      <c r="D518" s="2" t="s">
+      <c r="C518" t="s">
+        <v>7</v>
+      </c>
+      <c r="D518" s="1" t="s">
         <v>475</v>
       </c>
       <c r="E518" t="s">
@@ -11220,7 +12768,10 @@
       <c r="B519" t="s">
         <v>7</v>
       </c>
-      <c r="D519" s="2" t="s">
+      <c r="C519" t="s">
+        <v>7</v>
+      </c>
+      <c r="D519" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E519" t="s">
@@ -11237,7 +12788,10 @@
       <c r="B520" t="s">
         <v>7</v>
       </c>
-      <c r="D520" s="2" t="s">
+      <c r="C520" t="s">
+        <v>7</v>
+      </c>
+      <c r="D520" s="1" t="s">
         <v>477</v>
       </c>
       <c r="E520" t="s">
@@ -11254,7 +12808,10 @@
       <c r="B521" t="s">
         <v>7</v>
       </c>
-      <c r="D521" s="2" t="s">
+      <c r="C521" t="s">
+        <v>7</v>
+      </c>
+      <c r="D521" s="1" t="s">
         <v>478</v>
       </c>
       <c r="E521" t="s">
@@ -11271,7 +12828,10 @@
       <c r="B522" t="s">
         <v>7</v>
       </c>
-      <c r="D522" s="2" t="s">
+      <c r="C522" t="s">
+        <v>7</v>
+      </c>
+      <c r="D522" s="1" t="s">
         <v>479</v>
       </c>
       <c r="E522" t="s">
@@ -11288,7 +12848,10 @@
       <c r="B523" t="s">
         <v>7</v>
       </c>
-      <c r="D523" s="2" t="s">
+      <c r="C523" t="s">
+        <v>7</v>
+      </c>
+      <c r="D523" s="1" t="s">
         <v>480</v>
       </c>
       <c r="E523" t="s">
@@ -11305,7 +12868,10 @@
       <c r="B524" t="s">
         <v>7</v>
       </c>
-      <c r="D524" s="2" t="s">
+      <c r="C524" t="s">
+        <v>7</v>
+      </c>
+      <c r="D524" s="1" t="s">
         <v>481</v>
       </c>
       <c r="E524" t="s">
@@ -11322,7 +12888,10 @@
       <c r="B525" t="s">
         <v>7</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="C525" t="s">
+        <v>7</v>
+      </c>
+      <c r="D525" s="1" t="s">
         <v>482</v>
       </c>
       <c r="E525" t="s">
@@ -11339,7 +12908,10 @@
       <c r="B526" t="s">
         <v>7</v>
       </c>
-      <c r="D526" s="2" t="s">
+      <c r="C526" t="s">
+        <v>7</v>
+      </c>
+      <c r="D526" s="1" t="s">
         <v>483</v>
       </c>
       <c r="E526" t="s">
@@ -11356,7 +12928,10 @@
       <c r="B527" t="s">
         <v>7</v>
       </c>
-      <c r="D527" s="2" t="s">
+      <c r="C527" t="s">
+        <v>7</v>
+      </c>
+      <c r="D527" s="1" t="s">
         <v>484</v>
       </c>
       <c r="E527" t="s">
@@ -11373,7 +12948,10 @@
       <c r="B528" t="s">
         <v>7</v>
       </c>
-      <c r="D528" s="2" t="s">
+      <c r="C528" t="s">
+        <v>7</v>
+      </c>
+      <c r="D528" s="1" t="s">
         <v>485</v>
       </c>
       <c r="E528" t="s">
@@ -11390,7 +12968,10 @@
       <c r="B529" t="s">
         <v>7</v>
       </c>
-      <c r="D529" s="2" t="s">
+      <c r="C529" t="s">
+        <v>7</v>
+      </c>
+      <c r="D529" s="1" t="s">
         <v>486</v>
       </c>
       <c r="E529" t="s">
@@ -11407,7 +12988,10 @@
       <c r="B530" t="s">
         <v>7</v>
       </c>
-      <c r="D530" s="2" t="s">
+      <c r="C530" t="s">
+        <v>7</v>
+      </c>
+      <c r="D530" s="1" t="s">
         <v>487</v>
       </c>
       <c r="E530" t="s">
@@ -11424,7 +13008,10 @@
       <c r="B531" t="s">
         <v>7</v>
       </c>
-      <c r="D531" s="2" t="s">
+      <c r="C531" t="s">
+        <v>7</v>
+      </c>
+      <c r="D531" s="1" t="s">
         <v>488</v>
       </c>
       <c r="E531" t="s">
@@ -11441,7 +13028,10 @@
       <c r="B532" t="s">
         <v>7</v>
       </c>
-      <c r="D532" s="2" t="s">
+      <c r="C532" t="s">
+        <v>7</v>
+      </c>
+      <c r="D532" s="1" t="s">
         <v>489</v>
       </c>
       <c r="E532" t="s">
@@ -11458,7 +13048,10 @@
       <c r="B533" t="s">
         <v>7</v>
       </c>
-      <c r="D533" s="2" t="s">
+      <c r="C533" t="s">
+        <v>7</v>
+      </c>
+      <c r="D533" s="1" t="s">
         <v>490</v>
       </c>
       <c r="E533" t="s">
@@ -11475,7 +13068,10 @@
       <c r="B534" t="s">
         <v>7</v>
       </c>
-      <c r="D534" s="2" t="s">
+      <c r="C534" t="s">
+        <v>7</v>
+      </c>
+      <c r="D534" s="1" t="s">
         <v>491</v>
       </c>
       <c r="E534" t="s">
@@ -11492,7 +13088,10 @@
       <c r="B535" t="s">
         <v>7</v>
       </c>
-      <c r="D535" s="2" t="s">
+      <c r="C535" t="s">
+        <v>7</v>
+      </c>
+      <c r="D535" s="1" t="s">
         <v>492</v>
       </c>
       <c r="E535" t="s">
@@ -11509,7 +13108,10 @@
       <c r="B536" t="s">
         <v>7</v>
       </c>
-      <c r="D536" s="2" t="s">
+      <c r="C536" t="s">
+        <v>7</v>
+      </c>
+      <c r="D536" s="1" t="s">
         <v>493</v>
       </c>
       <c r="E536" t="s">
@@ -11526,7 +13128,10 @@
       <c r="B537" t="s">
         <v>7</v>
       </c>
-      <c r="D537" s="2" t="s">
+      <c r="C537" t="s">
+        <v>7</v>
+      </c>
+      <c r="D537" s="1" t="s">
         <v>494</v>
       </c>
       <c r="E537" t="s">
@@ -11543,7 +13148,10 @@
       <c r="B538" t="s">
         <v>7</v>
       </c>
-      <c r="D538" s="2" t="s">
+      <c r="C538" t="s">
+        <v>7</v>
+      </c>
+      <c r="D538" s="1" t="s">
         <v>495</v>
       </c>
       <c r="E538" t="s">
@@ -11560,7 +13168,10 @@
       <c r="B539" t="s">
         <v>7</v>
       </c>
-      <c r="D539" s="2" t="s">
+      <c r="C539" t="s">
+        <v>7</v>
+      </c>
+      <c r="D539" s="1" t="s">
         <v>496</v>
       </c>
       <c r="E539" t="s">
@@ -11577,7 +13188,10 @@
       <c r="B540" t="s">
         <v>7</v>
       </c>
-      <c r="D540" s="2" t="s">
+      <c r="C540" t="s">
+        <v>7</v>
+      </c>
+      <c r="D540" s="1" t="s">
         <v>497</v>
       </c>
       <c r="E540" t="s">
@@ -11594,7 +13208,10 @@
       <c r="B541" t="s">
         <v>7</v>
       </c>
-      <c r="D541" s="2" t="s">
+      <c r="C541" t="s">
+        <v>7</v>
+      </c>
+      <c r="D541" s="1" t="s">
         <v>498</v>
       </c>
       <c r="E541" t="s">
@@ -11611,7 +13228,10 @@
       <c r="B542" t="s">
         <v>7</v>
       </c>
-      <c r="D542" s="2" t="s">
+      <c r="C542" t="s">
+        <v>7</v>
+      </c>
+      <c r="D542" s="1" t="s">
         <v>499</v>
       </c>
       <c r="E542" t="s">
@@ -11628,7 +13248,10 @@
       <c r="B543" t="s">
         <v>7</v>
       </c>
-      <c r="D543" s="2" t="s">
+      <c r="C543" t="s">
+        <v>7</v>
+      </c>
+      <c r="D543" s="1" t="s">
         <v>500</v>
       </c>
       <c r="E543" t="s">
@@ -11645,7 +13268,10 @@
       <c r="B544" t="s">
         <v>7</v>
       </c>
-      <c r="D544" s="2" t="s">
+      <c r="C544" t="s">
+        <v>7</v>
+      </c>
+      <c r="D544" s="1" t="s">
         <v>501</v>
       </c>
       <c r="E544" t="s">
@@ -11662,7 +13288,10 @@
       <c r="B545" t="s">
         <v>7</v>
       </c>
-      <c r="D545" s="2" t="s">
+      <c r="C545" t="s">
+        <v>7</v>
+      </c>
+      <c r="D545" s="1" t="s">
         <v>502</v>
       </c>
       <c r="E545" t="s">
@@ -11679,7 +13308,10 @@
       <c r="B546" t="s">
         <v>7</v>
       </c>
-      <c r="D546" s="2" t="s">
+      <c r="C546" t="s">
+        <v>7</v>
+      </c>
+      <c r="D546" s="1" t="s">
         <v>503</v>
       </c>
       <c r="E546" t="s">
@@ -11696,7 +13328,10 @@
       <c r="B547" t="s">
         <v>7</v>
       </c>
-      <c r="D547" s="2" t="s">
+      <c r="C547" t="s">
+        <v>7</v>
+      </c>
+      <c r="D547" s="1" t="s">
         <v>504</v>
       </c>
       <c r="E547" t="s">
@@ -11713,7 +13348,10 @@
       <c r="B548" t="s">
         <v>7</v>
       </c>
-      <c r="D548" s="2" t="s">
+      <c r="C548" t="s">
+        <v>7</v>
+      </c>
+      <c r="D548" s="1" t="s">
         <v>505</v>
       </c>
       <c r="E548" t="s">
@@ -11730,7 +13368,10 @@
       <c r="B549" t="s">
         <v>7</v>
       </c>
-      <c r="D549" s="2" t="s">
+      <c r="C549" t="s">
+        <v>7</v>
+      </c>
+      <c r="D549" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E549" t="s">
@@ -11747,7 +13388,10 @@
       <c r="B550" t="s">
         <v>7</v>
       </c>
-      <c r="D550" s="2" t="s">
+      <c r="C550" t="s">
+        <v>7</v>
+      </c>
+      <c r="D550" s="1" t="s">
         <v>507</v>
       </c>
       <c r="E550" t="s">
@@ -11764,7 +13408,10 @@
       <c r="B551" t="s">
         <v>7</v>
       </c>
-      <c r="D551" s="2" t="s">
+      <c r="C551" t="s">
+        <v>7</v>
+      </c>
+      <c r="D551" s="1" t="s">
         <v>508</v>
       </c>
       <c r="E551" t="s">
@@ -11781,7 +13428,10 @@
       <c r="B552" t="s">
         <v>7</v>
       </c>
-      <c r="D552" s="2" t="s">
+      <c r="C552" t="s">
+        <v>7</v>
+      </c>
+      <c r="D552" s="1" t="s">
         <v>509</v>
       </c>
       <c r="E552" t="s">
@@ -11798,7 +13448,10 @@
       <c r="B553" t="s">
         <v>7</v>
       </c>
-      <c r="D553" s="2" t="s">
+      <c r="C553" t="s">
+        <v>7</v>
+      </c>
+      <c r="D553" s="1" t="s">
         <v>510</v>
       </c>
       <c r="E553" t="s">
@@ -11815,7 +13468,10 @@
       <c r="B554" t="s">
         <v>7</v>
       </c>
-      <c r="D554" s="2" t="s">
+      <c r="C554" t="s">
+        <v>7</v>
+      </c>
+      <c r="D554" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E554" t="s">
@@ -11832,7 +13488,10 @@
       <c r="B555" t="s">
         <v>7</v>
       </c>
-      <c r="D555" s="2" t="s">
+      <c r="C555" t="s">
+        <v>7</v>
+      </c>
+      <c r="D555" s="1" t="s">
         <v>512</v>
       </c>
       <c r="E555" t="s">
@@ -11849,7 +13508,10 @@
       <c r="B556" t="s">
         <v>7</v>
       </c>
-      <c r="D556" s="2" t="s">
+      <c r="C556" t="s">
+        <v>7</v>
+      </c>
+      <c r="D556" s="1" t="s">
         <v>513</v>
       </c>
       <c r="E556" t="s">
@@ -11866,7 +13528,10 @@
       <c r="B557" t="s">
         <v>7</v>
       </c>
-      <c r="D557" s="2" t="s">
+      <c r="C557" t="s">
+        <v>7</v>
+      </c>
+      <c r="D557" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E557" t="s">
@@ -11883,7 +13548,10 @@
       <c r="B558" t="s">
         <v>7</v>
       </c>
-      <c r="D558" s="2" t="s">
+      <c r="C558" t="s">
+        <v>7</v>
+      </c>
+      <c r="D558" s="1" t="s">
         <v>515</v>
       </c>
       <c r="E558" t="s">
@@ -11900,7 +13568,10 @@
       <c r="B559" t="s">
         <v>7</v>
       </c>
-      <c r="D559" s="2" t="s">
+      <c r="C559" t="s">
+        <v>7</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>516</v>
       </c>
       <c r="E559" t="s">
@@ -11917,7 +13588,10 @@
       <c r="B560" t="s">
         <v>7</v>
       </c>
-      <c r="D560" s="2" t="s">
+      <c r="C560" t="s">
+        <v>7</v>
+      </c>
+      <c r="D560" s="1" t="s">
         <v>517</v>
       </c>
       <c r="E560" t="s">
@@ -11934,7 +13608,10 @@
       <c r="B561" t="s">
         <v>7</v>
       </c>
-      <c r="D561" s="2" t="s">
+      <c r="C561" t="s">
+        <v>7</v>
+      </c>
+      <c r="D561" s="1" t="s">
         <v>518</v>
       </c>
       <c r="E561" t="s">
@@ -11951,7 +13628,10 @@
       <c r="B562" t="s">
         <v>7</v>
       </c>
-      <c r="D562" s="2" t="s">
+      <c r="C562" t="s">
+        <v>7</v>
+      </c>
+      <c r="D562" s="1" t="s">
         <v>519</v>
       </c>
       <c r="E562" t="s">
@@ -11968,7 +13648,10 @@
       <c r="B563" t="s">
         <v>7</v>
       </c>
-      <c r="D563" s="2" t="s">
+      <c r="C563" t="s">
+        <v>7</v>
+      </c>
+      <c r="D563" s="1" t="s">
         <v>520</v>
       </c>
       <c r="E563" t="s">
@@ -11985,7 +13668,10 @@
       <c r="B564" t="s">
         <v>7</v>
       </c>
-      <c r="D564" s="2" t="s">
+      <c r="C564" t="s">
+        <v>7</v>
+      </c>
+      <c r="D564" s="1" t="s">
         <v>521</v>
       </c>
       <c r="E564" t="s">
@@ -12002,7 +13688,10 @@
       <c r="B565" t="s">
         <v>7</v>
       </c>
-      <c r="D565" s="2" t="s">
+      <c r="C565" t="s">
+        <v>7</v>
+      </c>
+      <c r="D565" s="1" t="s">
         <v>522</v>
       </c>
       <c r="E565" t="s">
@@ -12019,7 +13708,10 @@
       <c r="B566" t="s">
         <v>7</v>
       </c>
-      <c r="D566" s="2" t="s">
+      <c r="C566" t="s">
+        <v>7</v>
+      </c>
+      <c r="D566" s="1" t="s">
         <v>523</v>
       </c>
       <c r="E566" t="s">
@@ -12036,7 +13728,10 @@
       <c r="B567" t="s">
         <v>7</v>
       </c>
-      <c r="D567" s="2" t="s">
+      <c r="C567" t="s">
+        <v>7</v>
+      </c>
+      <c r="D567" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E567" t="s">
@@ -12053,7 +13748,10 @@
       <c r="B568" t="s">
         <v>7</v>
       </c>
-      <c r="D568" s="2" t="s">
+      <c r="C568" t="s">
+        <v>7</v>
+      </c>
+      <c r="D568" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E568" t="s">
@@ -12070,7 +13768,10 @@
       <c r="B569" t="s">
         <v>7</v>
       </c>
-      <c r="D569" s="2" t="s">
+      <c r="C569" t="s">
+        <v>7</v>
+      </c>
+      <c r="D569" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E569" t="s">
@@ -12087,7 +13788,10 @@
       <c r="B570" t="s">
         <v>7</v>
       </c>
-      <c r="D570" s="2" t="s">
+      <c r="C570" t="s">
+        <v>7</v>
+      </c>
+      <c r="D570" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E570" t="s">
@@ -12104,7 +13808,10 @@
       <c r="B571" t="s">
         <v>7</v>
       </c>
-      <c r="D571" s="2" t="s">
+      <c r="C571" t="s">
+        <v>7</v>
+      </c>
+      <c r="D571" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E571" t="s">
@@ -12121,7 +13828,10 @@
       <c r="B572" t="s">
         <v>7</v>
       </c>
-      <c r="D572" s="2" t="s">
+      <c r="C572" t="s">
+        <v>7</v>
+      </c>
+      <c r="D572" s="1" t="s">
         <v>529</v>
       </c>
       <c r="E572" t="s">
@@ -12138,7 +13848,10 @@
       <c r="B573" t="s">
         <v>7</v>
       </c>
-      <c r="D573" s="2" t="s">
+      <c r="C573" t="s">
+        <v>7</v>
+      </c>
+      <c r="D573" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E573" t="s">
@@ -12155,7 +13868,10 @@
       <c r="B574" t="s">
         <v>7</v>
       </c>
-      <c r="D574" s="2" t="s">
+      <c r="C574" t="s">
+        <v>7</v>
+      </c>
+      <c r="D574" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E574" t="s">
@@ -12172,7 +13888,10 @@
       <c r="B575" t="s">
         <v>7</v>
       </c>
-      <c r="D575" s="2" t="s">
+      <c r="C575" t="s">
+        <v>7</v>
+      </c>
+      <c r="D575" s="1" t="s">
         <v>532</v>
       </c>
       <c r="E575" t="s">
@@ -12189,7 +13908,10 @@
       <c r="B576" t="s">
         <v>7</v>
       </c>
-      <c r="D576" s="2" t="s">
+      <c r="C576" t="s">
+        <v>7</v>
+      </c>
+      <c r="D576" s="1" t="s">
         <v>533</v>
       </c>
       <c r="E576" t="s">
@@ -12206,7 +13928,10 @@
       <c r="B577" t="s">
         <v>7</v>
       </c>
-      <c r="D577" s="2" t="s">
+      <c r="C577" t="s">
+        <v>7</v>
+      </c>
+      <c r="D577" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E577" t="s">
@@ -12223,7 +13948,10 @@
       <c r="B578" t="s">
         <v>7</v>
       </c>
-      <c r="D578" s="2" t="s">
+      <c r="C578" t="s">
+        <v>7</v>
+      </c>
+      <c r="D578" s="1" t="s">
         <v>535</v>
       </c>
       <c r="E578" t="s">
@@ -12240,7 +13968,10 @@
       <c r="B579" t="s">
         <v>7</v>
       </c>
-      <c r="D579" s="2" t="s">
+      <c r="C579" t="s">
+        <v>7</v>
+      </c>
+      <c r="D579" s="1" t="s">
         <v>536</v>
       </c>
       <c r="E579" t="s">
@@ -12257,7 +13988,10 @@
       <c r="B580" t="s">
         <v>7</v>
       </c>
-      <c r="D580" s="2" t="s">
+      <c r="C580" t="s">
+        <v>7</v>
+      </c>
+      <c r="D580" s="1" t="s">
         <v>537</v>
       </c>
       <c r="E580" t="s">
@@ -12274,7 +14008,10 @@
       <c r="B581" t="s">
         <v>7</v>
       </c>
-      <c r="D581" s="2" t="s">
+      <c r="C581" t="s">
+        <v>7</v>
+      </c>
+      <c r="D581" s="1" t="s">
         <v>538</v>
       </c>
       <c r="E581" t="s">
@@ -12291,7 +14028,10 @@
       <c r="B582" t="s">
         <v>7</v>
       </c>
-      <c r="D582" s="2" t="s">
+      <c r="C582" t="s">
+        <v>7</v>
+      </c>
+      <c r="D582" s="1" t="s">
         <v>539</v>
       </c>
       <c r="E582" t="s">
@@ -12308,7 +14048,10 @@
       <c r="B583" t="s">
         <v>7</v>
       </c>
-      <c r="D583" s="2" t="s">
+      <c r="C583" t="s">
+        <v>7</v>
+      </c>
+      <c r="D583" s="1" t="s">
         <v>540</v>
       </c>
       <c r="E583" t="s">
@@ -12325,7 +14068,10 @@
       <c r="B584" t="s">
         <v>7</v>
       </c>
-      <c r="D584" s="2" t="s">
+      <c r="C584" t="s">
+        <v>7</v>
+      </c>
+      <c r="D584" s="1" t="s">
         <v>541</v>
       </c>
       <c r="E584" t="s">
@@ -12342,7 +14088,10 @@
       <c r="B585" t="s">
         <v>7</v>
       </c>
-      <c r="D585" s="2" t="s">
+      <c r="C585" t="s">
+        <v>7</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>542</v>
       </c>
       <c r="E585" t="s">
@@ -12359,7 +14108,10 @@
       <c r="B586" t="s">
         <v>7</v>
       </c>
-      <c r="D586" s="2" t="s">
+      <c r="C586" t="s">
+        <v>7</v>
+      </c>
+      <c r="D586" s="1" t="s">
         <v>543</v>
       </c>
       <c r="E586" t="s">
@@ -12376,7 +14128,10 @@
       <c r="B587" t="s">
         <v>7</v>
       </c>
-      <c r="D587" s="2" t="s">
+      <c r="C587" t="s">
+        <v>7</v>
+      </c>
+      <c r="D587" s="1" t="s">
         <v>544</v>
       </c>
       <c r="E587" t="s">
@@ -12393,7 +14148,10 @@
       <c r="B588" t="s">
         <v>7</v>
       </c>
-      <c r="D588" s="2" t="s">
+      <c r="C588" t="s">
+        <v>7</v>
+      </c>
+      <c r="D588" s="1" t="s">
         <v>545</v>
       </c>
       <c r="E588" t="s">
@@ -12410,7 +14168,10 @@
       <c r="B589" t="s">
         <v>7</v>
       </c>
-      <c r="D589" s="2" t="s">
+      <c r="C589" t="s">
+        <v>7</v>
+      </c>
+      <c r="D589" s="1" t="s">
         <v>546</v>
       </c>
       <c r="E589" t="s">
@@ -12427,7 +14188,10 @@
       <c r="B590" t="s">
         <v>7</v>
       </c>
-      <c r="D590" s="2" t="s">
+      <c r="C590" t="s">
+        <v>7</v>
+      </c>
+      <c r="D590" s="1" t="s">
         <v>547</v>
       </c>
       <c r="E590" t="s">
@@ -12444,7 +14208,10 @@
       <c r="B591" t="s">
         <v>7</v>
       </c>
-      <c r="D591" s="2" t="s">
+      <c r="C591" t="s">
+        <v>7</v>
+      </c>
+      <c r="D591" s="1" t="s">
         <v>548</v>
       </c>
       <c r="E591" t="s">
@@ -12461,7 +14228,10 @@
       <c r="B592" t="s">
         <v>7</v>
       </c>
-      <c r="D592" s="2" t="s">
+      <c r="C592" t="s">
+        <v>7</v>
+      </c>
+      <c r="D592" s="1" t="s">
         <v>549</v>
       </c>
       <c r="E592" t="s">
@@ -12478,7 +14248,10 @@
       <c r="B593" t="s">
         <v>7</v>
       </c>
-      <c r="D593" s="2" t="s">
+      <c r="C593" t="s">
+        <v>7</v>
+      </c>
+      <c r="D593" s="1" t="s">
         <v>550</v>
       </c>
       <c r="E593" t="s">
@@ -12495,7 +14268,10 @@
       <c r="B594" t="s">
         <v>7</v>
       </c>
-      <c r="D594" s="2" t="s">
+      <c r="C594" t="s">
+        <v>7</v>
+      </c>
+      <c r="D594" s="1" t="s">
         <v>551</v>
       </c>
       <c r="E594" t="s">
@@ -12512,7 +14288,10 @@
       <c r="B595" t="s">
         <v>7</v>
       </c>
-      <c r="D595" s="2" t="s">
+      <c r="C595" t="s">
+        <v>7</v>
+      </c>
+      <c r="D595" s="1" t="s">
         <v>552</v>
       </c>
       <c r="E595" t="s">
@@ -12529,7 +14308,10 @@
       <c r="B596" t="s">
         <v>7</v>
       </c>
-      <c r="D596" s="2" t="s">
+      <c r="C596" t="s">
+        <v>7</v>
+      </c>
+      <c r="D596" s="1" t="s">
         <v>553</v>
       </c>
       <c r="E596" t="s">
@@ -12546,7 +14328,10 @@
       <c r="B597" t="s">
         <v>7</v>
       </c>
-      <c r="D597" s="2" t="s">
+      <c r="C597" t="s">
+        <v>7</v>
+      </c>
+      <c r="D597" s="1" t="s">
         <v>554</v>
       </c>
       <c r="E597" t="s">
@@ -12563,7 +14348,10 @@
       <c r="B598" t="s">
         <v>7</v>
       </c>
-      <c r="D598" s="2" t="s">
+      <c r="C598" t="s">
+        <v>7</v>
+      </c>
+      <c r="D598" s="1" t="s">
         <v>555</v>
       </c>
       <c r="E598" t="s">
@@ -12580,7 +14368,10 @@
       <c r="B599" t="s">
         <v>7</v>
       </c>
-      <c r="D599" s="2" t="s">
+      <c r="C599" t="s">
+        <v>7</v>
+      </c>
+      <c r="D599" s="1" t="s">
         <v>556</v>
       </c>
       <c r="E599" t="s">
@@ -12597,7 +14388,10 @@
       <c r="B600" t="s">
         <v>7</v>
       </c>
-      <c r="D600" s="2" t="s">
+      <c r="C600" t="s">
+        <v>7</v>
+      </c>
+      <c r="D600" s="1" t="s">
         <v>557</v>
       </c>
       <c r="E600" t="s">
@@ -12614,7 +14408,10 @@
       <c r="B601" t="s">
         <v>7</v>
       </c>
-      <c r="D601" s="2" t="s">
+      <c r="C601" t="s">
+        <v>7</v>
+      </c>
+      <c r="D601" s="1" t="s">
         <v>558</v>
       </c>
       <c r="E601" t="s">
@@ -12631,7 +14428,10 @@
       <c r="B602" t="s">
         <v>7</v>
       </c>
-      <c r="D602" s="2" t="s">
+      <c r="C602" t="s">
+        <v>7</v>
+      </c>
+      <c r="D602" s="1" t="s">
         <v>559</v>
       </c>
       <c r="E602" t="s">
@@ -12648,7 +14448,10 @@
       <c r="B603" t="s">
         <v>7</v>
       </c>
-      <c r="D603" s="2" t="s">
+      <c r="C603" t="s">
+        <v>7</v>
+      </c>
+      <c r="D603" s="1" t="s">
         <v>560</v>
       </c>
       <c r="E603" t="s">
@@ -12665,7 +14468,10 @@
       <c r="B604" t="s">
         <v>7</v>
       </c>
-      <c r="D604" s="2" t="s">
+      <c r="C604" t="s">
+        <v>7</v>
+      </c>
+      <c r="D604" s="1" t="s">
         <v>561</v>
       </c>
       <c r="E604" t="s">
@@ -12682,7 +14488,10 @@
       <c r="B605" t="s">
         <v>7</v>
       </c>
-      <c r="D605" s="2" t="s">
+      <c r="C605" t="s">
+        <v>7</v>
+      </c>
+      <c r="D605" s="1" t="s">
         <v>562</v>
       </c>
       <c r="E605" t="s">
@@ -12699,7 +14508,10 @@
       <c r="B606" t="s">
         <v>7</v>
       </c>
-      <c r="D606" s="2" t="s">
+      <c r="C606" t="s">
+        <v>7</v>
+      </c>
+      <c r="D606" s="1" t="s">
         <v>563</v>
       </c>
       <c r="E606" t="s">
@@ -12716,7 +14528,10 @@
       <c r="B607" t="s">
         <v>7</v>
       </c>
-      <c r="D607" s="2" t="s">
+      <c r="C607" t="s">
+        <v>7</v>
+      </c>
+      <c r="D607" s="1" t="s">
         <v>564</v>
       </c>
       <c r="E607" t="s">
@@ -12733,7 +14548,10 @@
       <c r="B608" t="s">
         <v>7</v>
       </c>
-      <c r="D608" s="2" t="s">
+      <c r="C608" t="s">
+        <v>7</v>
+      </c>
+      <c r="D608" s="1" t="s">
         <v>565</v>
       </c>
       <c r="E608" t="s">
@@ -12750,7 +14568,10 @@
       <c r="B609" t="s">
         <v>7</v>
       </c>
-      <c r="D609" s="2" t="s">
+      <c r="C609" t="s">
+        <v>7</v>
+      </c>
+      <c r="D609" s="1" t="s">
         <v>566</v>
       </c>
       <c r="E609" t="s">
@@ -12767,7 +14588,10 @@
       <c r="B610" t="s">
         <v>7</v>
       </c>
-      <c r="D610" s="2" t="s">
+      <c r="C610" t="s">
+        <v>7</v>
+      </c>
+      <c r="D610" s="1" t="s">
         <v>567</v>
       </c>
       <c r="E610" t="s">
@@ -12784,7 +14608,10 @@
       <c r="B611" t="s">
         <v>7</v>
       </c>
-      <c r="D611" s="2" t="s">
+      <c r="C611" t="s">
+        <v>7</v>
+      </c>
+      <c r="D611" s="1" t="s">
         <v>568</v>
       </c>
       <c r="E611" t="s">
@@ -12801,7 +14628,10 @@
       <c r="B612" t="s">
         <v>7</v>
       </c>
-      <c r="D612" s="2" t="s">
+      <c r="C612" t="s">
+        <v>7</v>
+      </c>
+      <c r="D612" s="1" t="s">
         <v>569</v>
       </c>
       <c r="E612" t="s">
@@ -12818,7 +14648,10 @@
       <c r="B613" t="s">
         <v>7</v>
       </c>
-      <c r="D613" s="2" t="s">
+      <c r="C613" t="s">
+        <v>7</v>
+      </c>
+      <c r="D613" s="1" t="s">
         <v>570</v>
       </c>
       <c r="E613" t="s">
@@ -12835,7 +14668,10 @@
       <c r="B614" t="s">
         <v>7</v>
       </c>
-      <c r="D614" s="2" t="s">
+      <c r="C614" t="s">
+        <v>7</v>
+      </c>
+      <c r="D614" s="1" t="s">
         <v>571</v>
       </c>
       <c r="E614" t="s">
@@ -12852,7 +14688,10 @@
       <c r="B615" t="s">
         <v>7</v>
       </c>
-      <c r="D615" s="2" t="s">
+      <c r="C615" t="s">
+        <v>7</v>
+      </c>
+      <c r="D615" s="1" t="s">
         <v>572</v>
       </c>
       <c r="E615" t="s">
@@ -12869,7 +14708,10 @@
       <c r="B616" t="s">
         <v>7</v>
       </c>
-      <c r="D616" s="2" t="s">
+      <c r="C616" t="s">
+        <v>7</v>
+      </c>
+      <c r="D616" s="1" t="s">
         <v>573</v>
       </c>
       <c r="E616" t="s">
@@ -12886,7 +14728,10 @@
       <c r="B617" t="s">
         <v>7</v>
       </c>
-      <c r="D617" s="2" t="s">
+      <c r="C617" t="s">
+        <v>7</v>
+      </c>
+      <c r="D617" s="1" t="s">
         <v>574</v>
       </c>
       <c r="E617" t="s">
@@ -12903,7 +14748,10 @@
       <c r="B618" t="s">
         <v>7</v>
       </c>
-      <c r="D618" s="2" t="s">
+      <c r="C618" t="s">
+        <v>7</v>
+      </c>
+      <c r="D618" s="1" t="s">
         <v>575</v>
       </c>
       <c r="E618" t="s">
@@ -12920,7 +14768,10 @@
       <c r="B619" t="s">
         <v>7</v>
       </c>
-      <c r="D619" s="2" t="s">
+      <c r="C619" t="s">
+        <v>7</v>
+      </c>
+      <c r="D619" s="1" t="s">
         <v>576</v>
       </c>
       <c r="E619" t="s">
@@ -12937,7 +14788,10 @@
       <c r="B620" t="s">
         <v>7</v>
       </c>
-      <c r="D620" s="2" t="s">
+      <c r="C620" t="s">
+        <v>7</v>
+      </c>
+      <c r="D620" s="1" t="s">
         <v>577</v>
       </c>
       <c r="E620" t="s">
@@ -12954,7 +14808,10 @@
       <c r="B621" t="s">
         <v>7</v>
       </c>
-      <c r="D621" s="2" t="s">
+      <c r="C621" t="s">
+        <v>7</v>
+      </c>
+      <c r="D621" s="1" t="s">
         <v>578</v>
       </c>
       <c r="E621" t="s">
@@ -12971,7 +14828,10 @@
       <c r="B622" t="s">
         <v>7</v>
       </c>
-      <c r="D622" s="2" t="s">
+      <c r="C622" t="s">
+        <v>7</v>
+      </c>
+      <c r="D622" s="1" t="s">
         <v>579</v>
       </c>
       <c r="E622" t="s">
@@ -12988,7 +14848,10 @@
       <c r="B623" t="s">
         <v>7</v>
       </c>
-      <c r="D623" s="2" t="s">
+      <c r="C623" t="s">
+        <v>7</v>
+      </c>
+      <c r="D623" s="1" t="s">
         <v>580</v>
       </c>
       <c r="E623" t="s">
@@ -13005,7 +14868,10 @@
       <c r="B624" t="s">
         <v>7</v>
       </c>
-      <c r="D624" s="2" t="s">
+      <c r="C624" t="s">
+        <v>7</v>
+      </c>
+      <c r="D624" s="1" t="s">
         <v>581</v>
       </c>
       <c r="E624" t="s">
@@ -13022,7 +14888,10 @@
       <c r="B625" t="s">
         <v>7</v>
       </c>
-      <c r="D625" s="2" t="s">
+      <c r="C625" t="s">
+        <v>7</v>
+      </c>
+      <c r="D625" s="1" t="s">
         <v>582</v>
       </c>
       <c r="E625" t="s">
@@ -13039,7 +14908,10 @@
       <c r="B626" t="s">
         <v>7</v>
       </c>
-      <c r="D626" s="2" t="s">
+      <c r="C626" t="s">
+        <v>7</v>
+      </c>
+      <c r="D626" s="1" t="s">
         <v>583</v>
       </c>
       <c r="E626" t="s">
@@ -13056,7 +14928,10 @@
       <c r="B627" t="s">
         <v>7</v>
       </c>
-      <c r="D627" s="2" t="s">
+      <c r="C627" t="s">
+        <v>7</v>
+      </c>
+      <c r="D627" s="1" t="s">
         <v>584</v>
       </c>
       <c r="E627" t="s">
@@ -13073,7 +14948,10 @@
       <c r="B628" t="s">
         <v>7</v>
       </c>
-      <c r="D628" s="2" t="s">
+      <c r="C628" t="s">
+        <v>7</v>
+      </c>
+      <c r="D628" s="1" t="s">
         <v>585</v>
       </c>
       <c r="E628" t="s">
@@ -13090,7 +14968,10 @@
       <c r="B629" t="s">
         <v>7</v>
       </c>
-      <c r="D629" s="2" t="s">
+      <c r="C629" t="s">
+        <v>7</v>
+      </c>
+      <c r="D629" s="1" t="s">
         <v>586</v>
       </c>
       <c r="E629" t="s">
@@ -13107,7 +14988,10 @@
       <c r="B630" t="s">
         <v>7</v>
       </c>
-      <c r="D630" s="2" t="s">
+      <c r="C630" t="s">
+        <v>7</v>
+      </c>
+      <c r="D630" s="1" t="s">
         <v>587</v>
       </c>
       <c r="E630" t="s">
@@ -13124,7 +15008,10 @@
       <c r="B631" t="s">
         <v>7</v>
       </c>
-      <c r="D631" s="2" t="s">
+      <c r="C631" t="s">
+        <v>7</v>
+      </c>
+      <c r="D631" s="1" t="s">
         <v>588</v>
       </c>
       <c r="E631" t="s">
@@ -13141,7 +15028,10 @@
       <c r="B632" t="s">
         <v>7</v>
       </c>
-      <c r="D632" s="2" t="s">
+      <c r="C632" t="s">
+        <v>7</v>
+      </c>
+      <c r="D632" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E632" t="s">
@@ -13158,7 +15048,10 @@
       <c r="B633" t="s">
         <v>7</v>
       </c>
-      <c r="D633" s="2" t="s">
+      <c r="C633" t="s">
+        <v>7</v>
+      </c>
+      <c r="D633" s="1" t="s">
         <v>590</v>
       </c>
       <c r="E633" t="s">
@@ -13175,7 +15068,10 @@
       <c r="B634" t="s">
         <v>7</v>
       </c>
-      <c r="D634" s="2" t="s">
+      <c r="C634" t="s">
+        <v>7</v>
+      </c>
+      <c r="D634" s="1" t="s">
         <v>591</v>
       </c>
       <c r="E634" t="s">
@@ -13192,7 +15088,10 @@
       <c r="B635" t="s">
         <v>7</v>
       </c>
-      <c r="D635" s="2" t="s">
+      <c r="C635" t="s">
+        <v>7</v>
+      </c>
+      <c r="D635" s="1" t="s">
         <v>592</v>
       </c>
       <c r="E635" t="s">
@@ -13209,7 +15108,10 @@
       <c r="B636" t="s">
         <v>7</v>
       </c>
-      <c r="D636" s="2" t="s">
+      <c r="C636" t="s">
+        <v>7</v>
+      </c>
+      <c r="D636" s="1" t="s">
         <v>593</v>
       </c>
       <c r="E636" t="s">
@@ -13226,7 +15128,10 @@
       <c r="B637" t="s">
         <v>7</v>
       </c>
-      <c r="D637" s="2" t="s">
+      <c r="C637" t="s">
+        <v>7</v>
+      </c>
+      <c r="D637" s="1" t="s">
         <v>594</v>
       </c>
       <c r="E637" t="s">
@@ -13243,7 +15148,10 @@
       <c r="B638" t="s">
         <v>7</v>
       </c>
-      <c r="D638" s="2" t="s">
+      <c r="C638" t="s">
+        <v>7</v>
+      </c>
+      <c r="D638" s="1" t="s">
         <v>595</v>
       </c>
       <c r="E638" t="s">
@@ -13260,7 +15168,10 @@
       <c r="B639" t="s">
         <v>7</v>
       </c>
-      <c r="D639" s="2" t="s">
+      <c r="C639" t="s">
+        <v>7</v>
+      </c>
+      <c r="D639" s="1" t="s">
         <v>596</v>
       </c>
       <c r="E639" t="s">
@@ -13277,7 +15188,10 @@
       <c r="B640" t="s">
         <v>7</v>
       </c>
-      <c r="D640" s="2" t="s">
+      <c r="C640" t="s">
+        <v>7</v>
+      </c>
+      <c r="D640" s="1" t="s">
         <v>597</v>
       </c>
       <c r="E640" t="s">
@@ -13294,7 +15208,10 @@
       <c r="B641" t="s">
         <v>7</v>
       </c>
-      <c r="D641" s="2" t="s">
+      <c r="C641" t="s">
+        <v>7</v>
+      </c>
+      <c r="D641" s="1" t="s">
         <v>598</v>
       </c>
       <c r="E641" t="s">
@@ -13311,7 +15228,10 @@
       <c r="B642" t="s">
         <v>7</v>
       </c>
-      <c r="D642" s="2" t="s">
+      <c r="C642" t="s">
+        <v>7</v>
+      </c>
+      <c r="D642" s="1" t="s">
         <v>599</v>
       </c>
       <c r="E642" t="s">
@@ -13328,7 +15248,10 @@
       <c r="B643" t="s">
         <v>7</v>
       </c>
-      <c r="D643" s="2" t="s">
+      <c r="C643" t="s">
+        <v>7</v>
+      </c>
+      <c r="D643" s="1" t="s">
         <v>600</v>
       </c>
       <c r="E643" t="s">
@@ -13345,7 +15268,10 @@
       <c r="B644" t="s">
         <v>7</v>
       </c>
-      <c r="D644" s="2" t="s">
+      <c r="C644" t="s">
+        <v>7</v>
+      </c>
+      <c r="D644" s="1" t="s">
         <v>601</v>
       </c>
       <c r="E644" t="s">
@@ -13362,7 +15288,10 @@
       <c r="B645" t="s">
         <v>7</v>
       </c>
-      <c r="D645" s="2" t="s">
+      <c r="C645" t="s">
+        <v>7</v>
+      </c>
+      <c r="D645" s="1" t="s">
         <v>602</v>
       </c>
       <c r="E645" t="s">
@@ -13379,7 +15308,10 @@
       <c r="B646" t="s">
         <v>7</v>
       </c>
-      <c r="D646" s="2" t="s">
+      <c r="C646" t="s">
+        <v>7</v>
+      </c>
+      <c r="D646" s="1" t="s">
         <v>603</v>
       </c>
       <c r="E646" t="s">
@@ -13396,7 +15328,10 @@
       <c r="B647" t="s">
         <v>7</v>
       </c>
-      <c r="D647" s="2" t="s">
+      <c r="C647" t="s">
+        <v>7</v>
+      </c>
+      <c r="D647" s="1" t="s">
         <v>604</v>
       </c>
       <c r="E647" t="s">
@@ -13413,7 +15348,10 @@
       <c r="B648" t="s">
         <v>7</v>
       </c>
-      <c r="D648" s="2" t="s">
+      <c r="C648" t="s">
+        <v>7</v>
+      </c>
+      <c r="D648" s="1" t="s">
         <v>605</v>
       </c>
       <c r="E648" t="s">
@@ -13430,7 +15368,10 @@
       <c r="B649" t="s">
         <v>7</v>
       </c>
-      <c r="D649" s="2" t="s">
+      <c r="C649" t="s">
+        <v>7</v>
+      </c>
+      <c r="D649" s="1" t="s">
         <v>606</v>
       </c>
       <c r="E649" t="s">
@@ -13447,7 +15388,10 @@
       <c r="B650" t="s">
         <v>7</v>
       </c>
-      <c r="D650" s="2" t="s">
+      <c r="C650" t="s">
+        <v>7</v>
+      </c>
+      <c r="D650" s="1" t="s">
         <v>607</v>
       </c>
       <c r="E650" t="s">
@@ -13464,7 +15408,10 @@
       <c r="B651" t="s">
         <v>7</v>
       </c>
-      <c r="D651" s="2" t="s">
+      <c r="C651" t="s">
+        <v>7</v>
+      </c>
+      <c r="D651" s="1" t="s">
         <v>608</v>
       </c>
       <c r="E651" t="s">
@@ -13481,7 +15428,10 @@
       <c r="B652" t="s">
         <v>7</v>
       </c>
-      <c r="D652" s="2" t="s">
+      <c r="C652" t="s">
+        <v>7</v>
+      </c>
+      <c r="D652" s="1" t="s">
         <v>609</v>
       </c>
       <c r="E652" t="s">
@@ -13498,7 +15448,10 @@
       <c r="B653" t="s">
         <v>7</v>
       </c>
-      <c r="D653" s="2" t="s">
+      <c r="C653" t="s">
+        <v>7</v>
+      </c>
+      <c r="D653" s="1" t="s">
         <v>610</v>
       </c>
       <c r="E653" t="s">
@@ -13515,7 +15468,10 @@
       <c r="B654" t="s">
         <v>7</v>
       </c>
-      <c r="D654" s="2" t="s">
+      <c r="C654" t="s">
+        <v>7</v>
+      </c>
+      <c r="D654" s="1" t="s">
         <v>611</v>
       </c>
       <c r="E654" t="s">
@@ -13532,7 +15488,10 @@
       <c r="B655" t="s">
         <v>7</v>
       </c>
-      <c r="D655" s="2" t="s">
+      <c r="C655" t="s">
+        <v>7</v>
+      </c>
+      <c r="D655" s="1" t="s">
         <v>612</v>
       </c>
       <c r="E655" t="s">
@@ -13549,7 +15508,10 @@
       <c r="B656" t="s">
         <v>7</v>
       </c>
-      <c r="D656" s="2" t="s">
+      <c r="C656" t="s">
+        <v>7</v>
+      </c>
+      <c r="D656" s="1" t="s">
         <v>613</v>
       </c>
       <c r="E656" t="s">
@@ -13566,7 +15528,10 @@
       <c r="B657" t="s">
         <v>7</v>
       </c>
-      <c r="D657" s="2" t="s">
+      <c r="C657" t="s">
+        <v>7</v>
+      </c>
+      <c r="D657" s="1" t="s">
         <v>614</v>
       </c>
       <c r="E657" t="s">
@@ -13583,7 +15548,10 @@
       <c r="B658" t="s">
         <v>7</v>
       </c>
-      <c r="D658" s="2" t="s">
+      <c r="C658" t="s">
+        <v>7</v>
+      </c>
+      <c r="D658" s="1" t="s">
         <v>615</v>
       </c>
       <c r="E658" t="s">
@@ -13600,7 +15568,10 @@
       <c r="B659" t="s">
         <v>7</v>
       </c>
-      <c r="D659" s="2" t="s">
+      <c r="C659" t="s">
+        <v>7</v>
+      </c>
+      <c r="D659" s="1" t="s">
         <v>616</v>
       </c>
       <c r="E659" t="s">
@@ -13617,7 +15588,10 @@
       <c r="B660" t="s">
         <v>7</v>
       </c>
-      <c r="D660" s="2" t="s">
+      <c r="C660" t="s">
+        <v>7</v>
+      </c>
+      <c r="D660" s="1" t="s">
         <v>617</v>
       </c>
       <c r="E660" t="s">
@@ -13634,7 +15608,10 @@
       <c r="B661" t="s">
         <v>7</v>
       </c>
-      <c r="D661" s="2" t="s">
+      <c r="C661" t="s">
+        <v>7</v>
+      </c>
+      <c r="D661" s="1" t="s">
         <v>618</v>
       </c>
       <c r="E661" t="s">
@@ -13651,7 +15628,10 @@
       <c r="B662" t="s">
         <v>7</v>
       </c>
-      <c r="D662" s="2" t="s">
+      <c r="C662" t="s">
+        <v>7</v>
+      </c>
+      <c r="D662" s="1" t="s">
         <v>619</v>
       </c>
       <c r="E662" t="s">
@@ -13668,7 +15648,10 @@
       <c r="B663" t="s">
         <v>7</v>
       </c>
-      <c r="D663" s="2" t="s">
+      <c r="C663" t="s">
+        <v>7</v>
+      </c>
+      <c r="D663" s="1" t="s">
         <v>620</v>
       </c>
       <c r="E663" t="s">
@@ -13685,7 +15668,10 @@
       <c r="B664" t="s">
         <v>7</v>
       </c>
-      <c r="D664" s="2" t="s">
+      <c r="C664" t="s">
+        <v>7</v>
+      </c>
+      <c r="D664" s="1" t="s">
         <v>621</v>
       </c>
       <c r="E664" t="s">
@@ -13702,7 +15688,10 @@
       <c r="B665" t="s">
         <v>7</v>
       </c>
-      <c r="D665" s="2" t="s">
+      <c r="C665" t="s">
+        <v>7</v>
+      </c>
+      <c r="D665" s="1" t="s">
         <v>622</v>
       </c>
       <c r="E665" t="s">
@@ -13719,7 +15708,10 @@
       <c r="B666" t="s">
         <v>7</v>
       </c>
-      <c r="D666" s="2" t="s">
+      <c r="C666" t="s">
+        <v>7</v>
+      </c>
+      <c r="D666" s="1" t="s">
         <v>623</v>
       </c>
       <c r="E666" t="s">
@@ -13736,7 +15728,10 @@
       <c r="B667" t="s">
         <v>7</v>
       </c>
-      <c r="D667" s="2" t="s">
+      <c r="C667" t="s">
+        <v>7</v>
+      </c>
+      <c r="D667" s="1" t="s">
         <v>624</v>
       </c>
       <c r="E667" t="s">
@@ -13753,7 +15748,10 @@
       <c r="B668" t="s">
         <v>7</v>
       </c>
-      <c r="D668" s="2" t="s">
+      <c r="C668" t="s">
+        <v>7</v>
+      </c>
+      <c r="D668" s="1" t="s">
         <v>625</v>
       </c>
       <c r="E668" t="s">
@@ -13770,7 +15768,10 @@
       <c r="B669" t="s">
         <v>7</v>
       </c>
-      <c r="D669" s="2" t="s">
+      <c r="C669" t="s">
+        <v>7</v>
+      </c>
+      <c r="D669" s="1" t="s">
         <v>626</v>
       </c>
       <c r="E669" t="s">
@@ -13787,7 +15788,10 @@
       <c r="B670" t="s">
         <v>7</v>
       </c>
-      <c r="D670" s="2" t="s">
+      <c r="C670" t="s">
+        <v>7</v>
+      </c>
+      <c r="D670" s="1" t="s">
         <v>627</v>
       </c>
       <c r="E670" t="s">
@@ -13804,7 +15808,10 @@
       <c r="B671" t="s">
         <v>7</v>
       </c>
-      <c r="D671" s="2" t="s">
+      <c r="C671" t="s">
+        <v>7</v>
+      </c>
+      <c r="D671" s="1" t="s">
         <v>628</v>
       </c>
       <c r="E671" t="s">
@@ -13821,7 +15828,10 @@
       <c r="B672" t="s">
         <v>7</v>
       </c>
-      <c r="D672" s="2" t="s">
+      <c r="C672" t="s">
+        <v>7</v>
+      </c>
+      <c r="D672" s="1" t="s">
         <v>629</v>
       </c>
       <c r="E672" t="s">
@@ -13838,7 +15848,10 @@
       <c r="B673" t="s">
         <v>7</v>
       </c>
-      <c r="D673" s="2" t="s">
+      <c r="C673" t="s">
+        <v>7</v>
+      </c>
+      <c r="D673" s="1" t="s">
         <v>630</v>
       </c>
       <c r="E673" t="s">
@@ -13855,7 +15868,10 @@
       <c r="B674" t="s">
         <v>7</v>
       </c>
-      <c r="D674" s="2" t="s">
+      <c r="C674" t="s">
+        <v>7</v>
+      </c>
+      <c r="D674" s="1" t="s">
         <v>631</v>
       </c>
       <c r="E674" t="s">
@@ -13872,7 +15888,10 @@
       <c r="B675" t="s">
         <v>7</v>
       </c>
-      <c r="D675" s="2" t="s">
+      <c r="C675" t="s">
+        <v>7</v>
+      </c>
+      <c r="D675" s="1" t="s">
         <v>632</v>
       </c>
       <c r="E675" t="s">
@@ -13889,7 +15908,10 @@
       <c r="B676" t="s">
         <v>7</v>
       </c>
-      <c r="D676" s="2" t="s">
+      <c r="C676" t="s">
+        <v>7</v>
+      </c>
+      <c r="D676" s="1" t="s">
         <v>633</v>
       </c>
       <c r="E676" t="s">
@@ -13906,7 +15928,10 @@
       <c r="B677" t="s">
         <v>7</v>
       </c>
-      <c r="D677" s="2" t="s">
+      <c r="C677" t="s">
+        <v>7</v>
+      </c>
+      <c r="D677" s="1" t="s">
         <v>634</v>
       </c>
       <c r="E677" t="s">
@@ -13923,7 +15948,10 @@
       <c r="B678" t="s">
         <v>7</v>
       </c>
-      <c r="D678" s="2" t="s">
+      <c r="C678" t="s">
+        <v>7</v>
+      </c>
+      <c r="D678" s="1" t="s">
         <v>635</v>
       </c>
       <c r="E678" t="s">
@@ -13940,7 +15968,10 @@
       <c r="B679" t="s">
         <v>7</v>
       </c>
-      <c r="D679" s="2" t="s">
+      <c r="C679" t="s">
+        <v>7</v>
+      </c>
+      <c r="D679" s="1" t="s">
         <v>636</v>
       </c>
       <c r="E679" t="s">
@@ -13957,7 +15988,10 @@
       <c r="B680" t="s">
         <v>7</v>
       </c>
-      <c r="D680" s="2" t="s">
+      <c r="C680" t="s">
+        <v>7</v>
+      </c>
+      <c r="D680" s="1" t="s">
         <v>637</v>
       </c>
       <c r="E680" t="s">
@@ -13974,7 +16008,10 @@
       <c r="B681" t="s">
         <v>7</v>
       </c>
-      <c r="D681" s="2" t="s">
+      <c r="C681" t="s">
+        <v>7</v>
+      </c>
+      <c r="D681" s="1" t="s">
         <v>638</v>
       </c>
       <c r="E681" t="s">
@@ -13991,7 +16028,10 @@
       <c r="B682" t="s">
         <v>7</v>
       </c>
-      <c r="D682" s="2" t="s">
+      <c r="C682" t="s">
+        <v>7</v>
+      </c>
+      <c r="D682" s="1" t="s">
         <v>639</v>
       </c>
       <c r="E682" t="s">
@@ -14008,7 +16048,10 @@
       <c r="B683" t="s">
         <v>7</v>
       </c>
-      <c r="D683" s="2" t="s">
+      <c r="C683" t="s">
+        <v>7</v>
+      </c>
+      <c r="D683" s="1" t="s">
         <v>640</v>
       </c>
       <c r="E683" t="s">
@@ -14025,7 +16068,10 @@
       <c r="B684" t="s">
         <v>7</v>
       </c>
-      <c r="D684" s="2" t="s">
+      <c r="C684" t="s">
+        <v>7</v>
+      </c>
+      <c r="D684" s="1" t="s">
         <v>641</v>
       </c>
       <c r="E684" t="s">
@@ -14042,7 +16088,10 @@
       <c r="B685" t="s">
         <v>7</v>
       </c>
-      <c r="D685" s="2" t="s">
+      <c r="C685" t="s">
+        <v>7</v>
+      </c>
+      <c r="D685" s="1" t="s">
         <v>642</v>
       </c>
       <c r="E685" t="s">
@@ -14059,7 +16108,10 @@
       <c r="B686" t="s">
         <v>7</v>
       </c>
-      <c r="D686" s="2" t="s">
+      <c r="C686" t="s">
+        <v>7</v>
+      </c>
+      <c r="D686" s="1" t="s">
         <v>643</v>
       </c>
       <c r="E686" t="s">
@@ -14076,7 +16128,10 @@
       <c r="B687" t="s">
         <v>7</v>
       </c>
-      <c r="D687" s="2" t="s">
+      <c r="C687" t="s">
+        <v>7</v>
+      </c>
+      <c r="D687" s="1" t="s">
         <v>644</v>
       </c>
       <c r="E687" t="s">
@@ -14093,7 +16148,10 @@
       <c r="B688" t="s">
         <v>7</v>
       </c>
-      <c r="D688" s="2" t="s">
+      <c r="C688" t="s">
+        <v>7</v>
+      </c>
+      <c r="D688" s="1" t="s">
         <v>645</v>
       </c>
       <c r="E688" t="s">
@@ -14110,7 +16168,10 @@
       <c r="B689" t="s">
         <v>7</v>
       </c>
-      <c r="D689" s="2" t="s">
+      <c r="C689" t="s">
+        <v>7</v>
+      </c>
+      <c r="D689" s="1" t="s">
         <v>646</v>
       </c>
       <c r="E689" t="s">
@@ -14127,7 +16188,10 @@
       <c r="B690" t="s">
         <v>7</v>
       </c>
-      <c r="D690" s="2" t="s">
+      <c r="C690" t="s">
+        <v>7</v>
+      </c>
+      <c r="D690" s="1" t="s">
         <v>647</v>
       </c>
       <c r="E690" t="s">
@@ -14144,7 +16208,10 @@
       <c r="B691" t="s">
         <v>7</v>
       </c>
-      <c r="D691" s="2" t="s">
+      <c r="C691" t="s">
+        <v>7</v>
+      </c>
+      <c r="D691" s="1" t="s">
         <v>648</v>
       </c>
       <c r="E691" t="s">
@@ -14161,7 +16228,10 @@
       <c r="B692" t="s">
         <v>7</v>
       </c>
-      <c r="D692" s="2" t="s">
+      <c r="C692" t="s">
+        <v>7</v>
+      </c>
+      <c r="D692" s="1" t="s">
         <v>649</v>
       </c>
       <c r="E692" t="s">
@@ -14178,7 +16248,10 @@
       <c r="B693" t="s">
         <v>7</v>
       </c>
-      <c r="D693" s="2" t="s">
+      <c r="C693" t="s">
+        <v>7</v>
+      </c>
+      <c r="D693" s="1" t="s">
         <v>650</v>
       </c>
       <c r="E693" t="s">
@@ -14195,7 +16268,10 @@
       <c r="B694" t="s">
         <v>7</v>
       </c>
-      <c r="D694" s="2" t="s">
+      <c r="C694" t="s">
+        <v>7</v>
+      </c>
+      <c r="D694" s="1" t="s">
         <v>651</v>
       </c>
       <c r="E694" t="s">
@@ -14212,7 +16288,10 @@
       <c r="B695" t="s">
         <v>7</v>
       </c>
-      <c r="D695" s="2" t="s">
+      <c r="C695" t="s">
+        <v>7</v>
+      </c>
+      <c r="D695" s="1" t="s">
         <v>652</v>
       </c>
       <c r="E695" t="s">
@@ -14229,7 +16308,10 @@
       <c r="B696" t="s">
         <v>7</v>
       </c>
-      <c r="D696" s="2" t="s">
+      <c r="C696" t="s">
+        <v>7</v>
+      </c>
+      <c r="D696" s="1" t="s">
         <v>653</v>
       </c>
       <c r="E696" t="s">
@@ -14246,7 +16328,10 @@
       <c r="B697" t="s">
         <v>7</v>
       </c>
-      <c r="D697" s="2" t="s">
+      <c r="C697" t="s">
+        <v>7</v>
+      </c>
+      <c r="D697" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E697" t="s">
@@ -14263,7 +16348,10 @@
       <c r="B698" t="s">
         <v>7</v>
       </c>
-      <c r="D698" s="2" t="s">
+      <c r="C698" t="s">
+        <v>7</v>
+      </c>
+      <c r="D698" s="1" t="s">
         <v>655</v>
       </c>
       <c r="E698" t="s">
@@ -14280,7 +16368,10 @@
       <c r="B699" t="s">
         <v>7</v>
       </c>
-      <c r="D699" s="2" t="s">
+      <c r="C699" t="s">
+        <v>7</v>
+      </c>
+      <c r="D699" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E699" t="s">
@@ -14297,7 +16388,10 @@
       <c r="B700" t="s">
         <v>7</v>
       </c>
-      <c r="D700" s="2" t="s">
+      <c r="C700" t="s">
+        <v>7</v>
+      </c>
+      <c r="D700" s="1" t="s">
         <v>657</v>
       </c>
       <c r="E700" t="s">
